--- a/Duty Roaster for Mid Term.xlsx
+++ b/Duty Roaster for Mid Term.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Control Room NPI\MID TERM JUNE-2026\Gemini Duty Roster  Teacher list,hall super\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65870468-31BD-4C60-BCE9-B7B5F4423F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64D1A3B-9B4A-4CFF-A389-F049F64FEBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Chief Invigilators" sheetId="8" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Chief Invigilators'!$A$2:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Hallsupers'!$A$2:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Hallsupers'!$A$2:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Teachers'!$A$2:$C$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'MLSS Roaster'!$A$2:$C$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'All Teachers'!$1:$3</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="87">
   <si>
     <t>Designation</t>
   </si>
@@ -661,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -731,18 +731,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -873,6 +867,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1250,200 +1247,200 @@
     <col min="1" max="1" width="4.1640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="40" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="38" customWidth="1"/>
     <col min="5" max="32" width="5.33203125" style="8" customWidth="1"/>
     <col min="33" max="36" width="8.83203125" style="2"/>
     <col min="37" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="74"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="73"/>
     </row>
     <row r="2" spans="1:35" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="71">
+      <c r="E2" s="70">
         <v>46180</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71">
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70">
         <v>46181</v>
       </c>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71">
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70">
         <v>46182</v>
       </c>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71">
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70">
         <v>46183</v>
       </c>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71">
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70">
         <v>46184</v>
       </c>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71">
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
+      <c r="Y2" s="70">
         <v>46187</v>
       </c>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71">
+      <c r="Z2" s="70"/>
+      <c r="AA2" s="70"/>
+      <c r="AB2" s="70"/>
+      <c r="AC2" s="70">
         <v>46188</v>
       </c>
-      <c r="AD2" s="71"/>
-      <c r="AE2" s="71"/>
-      <c r="AF2" s="71"/>
-      <c r="AG2" s="72" t="s">
+      <c r="AD2" s="70"/>
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="71" t="s">
         <v>63</v>
       </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
     </row>
     <row r="3" spans="1:35" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="32">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="F3" s="7">
         <v>11</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="30">
         <v>12.3</v>
       </c>
       <c r="H3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="J3" s="7">
         <v>11</v>
       </c>
-      <c r="K3" s="32">
+      <c r="K3" s="30">
         <v>12.3</v>
       </c>
       <c r="L3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M3" s="32">
+      <c r="M3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="N3" s="7">
         <v>11</v>
       </c>
-      <c r="O3" s="32">
+      <c r="O3" s="30">
         <v>12.3</v>
       </c>
       <c r="P3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Q3" s="32">
+      <c r="Q3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="R3" s="7">
         <v>11</v>
       </c>
-      <c r="S3" s="32">
+      <c r="S3" s="30">
         <v>12.3</v>
       </c>
       <c r="T3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="U3" s="32">
+      <c r="U3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="V3" s="7">
         <v>11</v>
       </c>
-      <c r="W3" s="32">
+      <c r="W3" s="30">
         <v>12.3</v>
       </c>
       <c r="X3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Y3" s="32">
+      <c r="Y3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="Z3" s="7">
         <v>11</v>
       </c>
-      <c r="AA3" s="32">
+      <c r="AA3" s="30">
         <v>12.3</v>
       </c>
       <c r="AB3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AC3" s="32">
+      <c r="AC3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="AD3" s="7">
         <v>11</v>
       </c>
-      <c r="AE3" s="32">
+      <c r="AE3" s="30">
         <v>12.3</v>
       </c>
       <c r="AF3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AG3" s="72"/>
+      <c r="AG3" s="71"/>
     </row>
     <row r="4" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
@@ -1455,144 +1452,144 @@
       <c r="C4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="48">
-        <v>1</v>
-      </c>
-      <c r="F4" s="41">
-        <v>1</v>
-      </c>
-      <c r="G4" s="45"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="48">
-        <v>1</v>
-      </c>
-      <c r="J4" s="41">
-        <v>1</v>
-      </c>
-      <c r="K4" s="45"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="48">
-        <v>1</v>
-      </c>
-      <c r="N4" s="41">
-        <v>1</v>
-      </c>
-      <c r="O4" s="45"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="48">
-        <v>1</v>
-      </c>
-      <c r="R4" s="41">
-        <v>1</v>
-      </c>
-      <c r="S4" s="45"/>
-      <c r="T4" s="53"/>
-      <c r="U4" s="48">
-        <v>1</v>
-      </c>
-      <c r="V4" s="41">
-        <v>1</v>
-      </c>
-      <c r="W4" s="45"/>
-      <c r="X4" s="53"/>
-      <c r="Y4" s="48">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="41">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="45">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="53"/>
-      <c r="AC4" s="48">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="41">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="45"/>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="27">
+      <c r="E4" s="46">
+        <v>1</v>
+      </c>
+      <c r="F4" s="39">
+        <v>1</v>
+      </c>
+      <c r="G4" s="43"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="46">
+        <v>1</v>
+      </c>
+      <c r="J4" s="39">
+        <v>1</v>
+      </c>
+      <c r="K4" s="43"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="46">
+        <v>1</v>
+      </c>
+      <c r="N4" s="39">
+        <v>1</v>
+      </c>
+      <c r="O4" s="43"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="46">
+        <v>1</v>
+      </c>
+      <c r="R4" s="39">
+        <v>1</v>
+      </c>
+      <c r="S4" s="43"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="46">
+        <v>1</v>
+      </c>
+      <c r="V4" s="39">
+        <v>1</v>
+      </c>
+      <c r="W4" s="43"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="46">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="39">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="43">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="46">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="39">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="43"/>
+      <c r="AF4" s="51"/>
+      <c r="AG4" s="25">
         <f>SUM(E4:AF4)</f>
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24">
+      <c r="A5" s="23">
         <v>2</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="46">
-        <v>1</v>
-      </c>
-      <c r="H5" s="54">
-        <v>1</v>
-      </c>
-      <c r="I5" s="49"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="46">
-        <v>1</v>
-      </c>
-      <c r="L5" s="54">
-        <v>1</v>
-      </c>
-      <c r="M5" s="49"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="46">
-        <v>1</v>
-      </c>
-      <c r="P5" s="54">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="49">
-        <v>1</v>
-      </c>
-      <c r="R5" s="42"/>
-      <c r="S5" s="46">
-        <v>1</v>
-      </c>
-      <c r="T5" s="54">
-        <v>1</v>
-      </c>
-      <c r="U5" s="49"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="46">
-        <v>1</v>
-      </c>
-      <c r="X5" s="54">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="46">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="54">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="49"/>
-      <c r="AD5" s="42"/>
-      <c r="AE5" s="46">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="54">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="28">
+      <c r="E5" s="47"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="44">
+        <v>1</v>
+      </c>
+      <c r="H5" s="52">
+        <v>1</v>
+      </c>
+      <c r="I5" s="47"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="44">
+        <v>1</v>
+      </c>
+      <c r="L5" s="52">
+        <v>1</v>
+      </c>
+      <c r="M5" s="47"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="44">
+        <v>1</v>
+      </c>
+      <c r="P5" s="52">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="47">
+        <v>1</v>
+      </c>
+      <c r="R5" s="40"/>
+      <c r="S5" s="44">
+        <v>1</v>
+      </c>
+      <c r="T5" s="52">
+        <v>1</v>
+      </c>
+      <c r="U5" s="47"/>
+      <c r="V5" s="40"/>
+      <c r="W5" s="44">
+        <v>1</v>
+      </c>
+      <c r="X5" s="52">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="40"/>
+      <c r="AA5" s="44">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="52">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="40"/>
+      <c r="AE5" s="44">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="52">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="26">
         <f>SUM(E5:AF5)</f>
         <v>15</v>
       </c>
@@ -1601,120 +1598,120 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="51">
+      <c r="D6" s="38"/>
+      <c r="E6" s="49">
         <f>SUM(E4:E5)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="49">
         <f t="shared" ref="F6:AF6" si="0">SUM(F4:F5)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="P6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="51">
+      <c r="G6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="49">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="T6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="U6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="V6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="W6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Z6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA6" s="51">
+      <c r="R6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA6" s="49">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AB6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF6" s="51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AG6" s="51">
+      <c r="AB6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF6" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AG6" s="49">
         <f>SUM(AG4:AG5)</f>
         <v>30</v>
       </c>
@@ -1751,7 +1748,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" style="3" customWidth="1"/>
@@ -1764,206 +1761,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="74"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="73"/>
     </row>
     <row r="2" spans="1:35" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="71">
+      <c r="E2" s="70">
         <v>46180</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71">
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70">
         <v>46181</v>
       </c>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71">
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70">
         <v>46182</v>
       </c>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71">
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70">
         <v>46183</v>
       </c>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71">
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70">
         <v>46184</v>
       </c>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71">
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
+      <c r="Y2" s="70">
         <v>46187</v>
       </c>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71">
+      <c r="Z2" s="70"/>
+      <c r="AA2" s="70"/>
+      <c r="AB2" s="70"/>
+      <c r="AC2" s="70">
         <v>46188</v>
       </c>
-      <c r="AD2" s="71"/>
-      <c r="AE2" s="71"/>
-      <c r="AF2" s="71"/>
-      <c r="AG2" s="72" t="s">
+      <c r="AD2" s="70"/>
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="71" t="s">
         <v>63</v>
       </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
     </row>
-    <row r="3" spans="1:35" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="32">
+    <row r="3" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="F3" s="7">
         <v>11</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="30">
         <v>12.3</v>
       </c>
       <c r="H3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="J3" s="7">
         <v>11</v>
       </c>
-      <c r="K3" s="32">
+      <c r="K3" s="30">
         <v>12.3</v>
       </c>
       <c r="L3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M3" s="32">
+      <c r="M3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="N3" s="7">
         <v>11</v>
       </c>
-      <c r="O3" s="32">
+      <c r="O3" s="30">
         <v>12.3</v>
       </c>
       <c r="P3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Q3" s="32">
+      <c r="Q3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="R3" s="7">
         <v>11</v>
       </c>
-      <c r="S3" s="32">
+      <c r="S3" s="30">
         <v>12.3</v>
       </c>
       <c r="T3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="U3" s="32">
+      <c r="U3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="V3" s="7">
         <v>11</v>
       </c>
-      <c r="W3" s="32">
+      <c r="W3" s="30">
         <v>12.3</v>
       </c>
       <c r="X3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Y3" s="32">
+      <c r="Y3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="Z3" s="7">
         <v>11</v>
       </c>
-      <c r="AA3" s="32">
+      <c r="AA3" s="30">
         <v>12.3</v>
       </c>
       <c r="AB3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AC3" s="32">
+      <c r="AC3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="AD3" s="7">
         <v>11</v>
       </c>
-      <c r="AE3" s="32">
+      <c r="AE3" s="30">
         <v>12.3</v>
       </c>
       <c r="AF3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AG3" s="72"/>
+      <c r="AG3" s="71"/>
     </row>
     <row r="4" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20">
-        <v>1</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>78</v>
+      <c r="A4" s="16">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>2</v>
       </c>
       <c r="E4" s="48">
         <v>1</v>
@@ -1971,7 +1968,9 @@
       <c r="F4" s="41">
         <v>1</v>
       </c>
-      <c r="G4" s="45"/>
+      <c r="G4" s="45">
+        <v>1</v>
+      </c>
       <c r="H4" s="53"/>
       <c r="I4" s="48">
         <v>1</v>
@@ -1980,7 +1979,9 @@
         <v>1</v>
       </c>
       <c r="K4" s="45"/>
-      <c r="L4" s="53"/>
+      <c r="L4" s="53">
+        <v>1</v>
+      </c>
       <c r="M4" s="48">
         <v>1</v>
       </c>
@@ -2000,14 +2001,10 @@
       <c r="U4" s="48">
         <v>1</v>
       </c>
-      <c r="V4" s="41">
-        <v>1</v>
-      </c>
+      <c r="V4" s="41"/>
       <c r="W4" s="45"/>
       <c r="X4" s="53"/>
-      <c r="Y4" s="48">
-        <v>1</v>
-      </c>
+      <c r="Y4" s="48"/>
       <c r="Z4" s="41">
         <v>1</v>
       </c>
@@ -2018,468 +2015,464 @@
       <c r="AC4" s="48">
         <v>1</v>
       </c>
-      <c r="AD4" s="41">
-        <v>1</v>
-      </c>
+      <c r="AD4" s="41"/>
       <c r="AE4" s="45"/>
       <c r="AF4" s="53"/>
       <c r="AG4" s="27">
         <f>SUM(E4:AF4)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
         <v>2</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="58" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>3</v>
+      <c r="B5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="E5" s="49"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="46">
+      <c r="F5" s="42">
+        <v>1</v>
+      </c>
+      <c r="G5" s="12">
         <v>1</v>
       </c>
       <c r="H5" s="54">
         <v>1</v>
       </c>
-      <c r="I5" s="49"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="46">
-        <v>1</v>
-      </c>
-      <c r="L5" s="54">
-        <v>1</v>
-      </c>
-      <c r="M5" s="49"/>
+      <c r="I5" s="49">
+        <v>1</v>
+      </c>
+      <c r="J5" s="42">
+        <v>1</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="49">
+        <v>1</v>
+      </c>
       <c r="N5" s="42"/>
-      <c r="O5" s="46">
-        <v>1</v>
-      </c>
-      <c r="P5" s="54">
-        <v>1</v>
-      </c>
+      <c r="O5" s="12"/>
+      <c r="P5" s="54"/>
       <c r="Q5" s="49">
         <v>1</v>
       </c>
       <c r="R5" s="42"/>
-      <c r="S5" s="46">
+      <c r="S5" s="12">
         <v>1</v>
       </c>
       <c r="T5" s="54">
         <v>1</v>
       </c>
-      <c r="U5" s="49"/>
+      <c r="U5" s="49">
+        <v>1</v>
+      </c>
       <c r="V5" s="42"/>
-      <c r="W5" s="46">
-        <v>1</v>
-      </c>
-      <c r="X5" s="54">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="46">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="54">
-        <v>1</v>
-      </c>
+      <c r="W5" s="12">
+        <v>1</v>
+      </c>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="42">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="54"/>
       <c r="AC5" s="49"/>
       <c r="AD5" s="42"/>
-      <c r="AE5" s="46">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="54">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="28">
-        <f>SUM(E5:AF5)</f>
-        <v>15</v>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="54"/>
+      <c r="AG5" s="13">
+        <f t="shared" ref="AG5:AG10" si="0">SUM(E5:AF5)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="18" t="s">
+      <c r="B6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="50">
-        <v>1</v>
-      </c>
-      <c r="F6" s="43">
-        <v>1</v>
-      </c>
-      <c r="G6" s="47">
-        <v>1</v>
-      </c>
-      <c r="H6" s="55"/>
-      <c r="I6" s="50">
-        <v>1</v>
-      </c>
-      <c r="J6" s="43">
-        <v>1</v>
-      </c>
-      <c r="K6" s="47"/>
-      <c r="L6" s="55">
-        <v>1</v>
-      </c>
-      <c r="M6" s="50">
-        <v>1</v>
-      </c>
-      <c r="N6" s="43">
-        <v>1</v>
-      </c>
-      <c r="O6" s="47"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="50">
-        <v>1</v>
-      </c>
-      <c r="R6" s="43">
-        <v>1</v>
-      </c>
-      <c r="S6" s="47"/>
-      <c r="T6" s="55"/>
-      <c r="U6" s="50">
-        <v>1</v>
-      </c>
-      <c r="V6" s="43"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="50"/>
-      <c r="Z6" s="43">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="47">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="55"/>
-      <c r="AC6" s="50">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="47"/>
-      <c r="AF6" s="55"/>
-      <c r="AG6" s="29">
-        <f>SUM(E6:AF6)</f>
+      <c r="D6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="49">
+        <v>1</v>
+      </c>
+      <c r="F6" s="42">
+        <v>1</v>
+      </c>
+      <c r="G6" s="12">
+        <v>1</v>
+      </c>
+      <c r="H6" s="54"/>
+      <c r="I6" s="49">
+        <v>1</v>
+      </c>
+      <c r="J6" s="42">
+        <v>1</v>
+      </c>
+      <c r="K6" s="12">
+        <v>1</v>
+      </c>
+      <c r="L6" s="54"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="42">
+        <v>1</v>
+      </c>
+      <c r="O6" s="12">
+        <v>1</v>
+      </c>
+      <c r="P6" s="54">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>1</v>
+      </c>
+      <c r="R6" s="42"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="54">
+        <v>1</v>
+      </c>
+      <c r="U6" s="49">
+        <v>1</v>
+      </c>
+      <c r="V6" s="42"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="42">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="42"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="54"/>
+      <c r="AG6" s="13">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14">
+      <c r="A7" s="69">
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="49">
+        <v>1</v>
+      </c>
+      <c r="F7" s="42">
+        <v>1</v>
+      </c>
+      <c r="G7" s="12">
+        <v>1</v>
+      </c>
+      <c r="H7" s="54">
+        <v>1</v>
+      </c>
+      <c r="I7" s="49"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="49">
+        <v>1</v>
+      </c>
+      <c r="R7" s="42">
+        <v>1</v>
+      </c>
+      <c r="S7" s="12">
+        <v>1</v>
+      </c>
+      <c r="T7" s="54"/>
+      <c r="U7" s="49">
+        <v>1</v>
+      </c>
+      <c r="V7" s="42"/>
+      <c r="W7" s="12">
+        <v>1</v>
+      </c>
+      <c r="X7" s="54">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="42">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="54">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="42"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="54"/>
+      <c r="AG7" s="13">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="16">
         <v>5</v>
       </c>
-      <c r="E7" s="51">
-        <v>1</v>
-      </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="12">
-        <v>1</v>
-      </c>
-      <c r="H7" s="56">
-        <v>1</v>
-      </c>
-      <c r="I7" s="51">
-        <v>1</v>
-      </c>
-      <c r="J7" s="44">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="51">
-        <v>1</v>
-      </c>
-      <c r="N7" s="44"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="51">
-        <v>1</v>
-      </c>
-      <c r="R7" s="44"/>
-      <c r="S7" s="12">
-        <v>1</v>
-      </c>
-      <c r="T7" s="56">
-        <v>1</v>
-      </c>
-      <c r="U7" s="51">
-        <v>1</v>
-      </c>
-      <c r="V7" s="44"/>
-      <c r="W7" s="12">
-        <v>1</v>
-      </c>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="44">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="56"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="12"/>
-      <c r="AF7" s="56"/>
-      <c r="AG7" s="13">
-        <f t="shared" ref="AG7:AG12" si="0">SUM(E7:AF7)</f>
+      <c r="B8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="50">
+        <v>1</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="50">
+        <v>1</v>
+      </c>
+      <c r="J8" s="42"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="55">
+        <v>1</v>
+      </c>
+      <c r="M8" s="50">
+        <v>1</v>
+      </c>
+      <c r="N8" s="42"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="55">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="50">
+        <v>1</v>
+      </c>
+      <c r="R8" s="42"/>
+      <c r="S8" s="12">
+        <v>1</v>
+      </c>
+      <c r="T8" s="55"/>
+      <c r="U8" s="50">
+        <v>1</v>
+      </c>
+      <c r="V8" s="42"/>
+      <c r="W8" s="12">
+        <v>1</v>
+      </c>
+      <c r="X8" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="42"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="55"/>
+      <c r="AC8" s="50">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="42"/>
+      <c r="AE8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="55">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="13">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="51">
-        <v>1</v>
-      </c>
-      <c r="F8" s="44">
-        <v>1</v>
-      </c>
-      <c r="G8" s="12">
-        <v>1</v>
-      </c>
-      <c r="H8" s="56"/>
-      <c r="I8" s="51">
-        <v>1</v>
-      </c>
-      <c r="J8" s="44">
-        <v>1</v>
-      </c>
-      <c r="K8" s="12">
-        <v>1</v>
-      </c>
-      <c r="L8" s="56"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="44">
-        <v>1</v>
-      </c>
-      <c r="O8" s="12">
-        <v>1</v>
-      </c>
-      <c r="P8" s="56">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="51">
-        <v>1</v>
-      </c>
-      <c r="R8" s="44"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="56">
-        <v>1</v>
-      </c>
-      <c r="U8" s="51">
-        <v>1</v>
-      </c>
-      <c r="V8" s="44"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="44">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="44"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="13">
+    <row r="9" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="69">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="49"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="54">
+        <v>1</v>
+      </c>
+      <c r="I9" s="49"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="12">
+        <v>1</v>
+      </c>
+      <c r="L9" s="54"/>
+      <c r="M9" s="49">
+        <v>1</v>
+      </c>
+      <c r="N9" s="42">
+        <v>1</v>
+      </c>
+      <c r="O9" s="12">
+        <v>1</v>
+      </c>
+      <c r="P9" s="54">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="49">
+        <v>1</v>
+      </c>
+      <c r="R9" s="42"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="54">
+        <v>1</v>
+      </c>
+      <c r="U9" s="49">
+        <v>1</v>
+      </c>
+      <c r="V9" s="42">
+        <v>1</v>
+      </c>
+      <c r="W9" s="12"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="42"/>
+      <c r="AA9" s="12"/>
+      <c r="AB9" s="54">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="42">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="54">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="13">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="51">
-        <v>1</v>
-      </c>
-      <c r="F9" s="44">
-        <v>1</v>
-      </c>
-      <c r="G9" s="12">
-        <v>1</v>
-      </c>
-      <c r="H9" s="56">
-        <v>1</v>
-      </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="51">
-        <v>1</v>
-      </c>
-      <c r="R9" s="44">
-        <v>1</v>
-      </c>
-      <c r="S9" s="12">
-        <v>1</v>
-      </c>
-      <c r="T9" s="56"/>
-      <c r="U9" s="51">
-        <v>1</v>
-      </c>
-      <c r="V9" s="44"/>
-      <c r="W9" s="12">
-        <v>1</v>
-      </c>
-      <c r="X9" s="56">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="44">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="56">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="44"/>
-      <c r="AE9" s="12"/>
-      <c r="AF9" s="56"/>
-      <c r="AG9" s="13">
+    <row r="10" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="49"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="54">
+        <v>1</v>
+      </c>
+      <c r="I10" s="49"/>
+      <c r="J10" s="42">
+        <v>1</v>
+      </c>
+      <c r="K10" s="12">
+        <v>1</v>
+      </c>
+      <c r="L10" s="54">
+        <v>1</v>
+      </c>
+      <c r="M10" s="49">
+        <v>1</v>
+      </c>
+      <c r="N10" s="42">
+        <v>1</v>
+      </c>
+      <c r="O10" s="12">
+        <v>1</v>
+      </c>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="42">
+        <v>1</v>
+      </c>
+      <c r="S10" s="12"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="42">
+        <v>1</v>
+      </c>
+      <c r="W10" s="12"/>
+      <c r="X10" s="54">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="42">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="49"/>
+      <c r="AD10" s="42"/>
+      <c r="AE10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="54">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="13">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="44">
-        <v>1</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="52">
-        <v>1</v>
-      </c>
-      <c r="J10" s="44"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="57">
-        <v>1</v>
-      </c>
-      <c r="M10" s="52">
-        <v>1</v>
-      </c>
-      <c r="N10" s="44"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="57">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="52">
-        <v>1</v>
-      </c>
-      <c r="R10" s="44"/>
-      <c r="S10" s="12">
-        <v>1</v>
-      </c>
-      <c r="T10" s="57"/>
-      <c r="U10" s="52">
-        <v>1</v>
-      </c>
-      <c r="V10" s="44"/>
-      <c r="W10" s="12">
-        <v>1</v>
-      </c>
-      <c r="X10" s="57">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="52">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="57"/>
-      <c r="AC10" s="52">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="57">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="13">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
     <row r="11" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="14">
+      <c r="A11" s="69">
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>6</v>
@@ -2487,341 +2480,193 @@
       <c r="D11" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="44"/>
+      <c r="E11" s="49">
+        <v>1</v>
+      </c>
+      <c r="F11" s="42"/>
       <c r="G11" s="12"/>
-      <c r="H11" s="56">
-        <v>1</v>
-      </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="44"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="49">
+        <v>1</v>
+      </c>
+      <c r="J11" s="42">
+        <v>1</v>
+      </c>
       <c r="K11" s="12">
         <v>1</v>
       </c>
-      <c r="L11" s="56"/>
-      <c r="M11" s="51">
-        <v>1</v>
-      </c>
-      <c r="N11" s="44">
-        <v>1</v>
-      </c>
+      <c r="L11" s="54">
+        <v>1</v>
+      </c>
+      <c r="M11" s="49"/>
+      <c r="N11" s="42"/>
       <c r="O11" s="12">
         <v>1</v>
       </c>
-      <c r="P11" s="56">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="51">
-        <v>1</v>
-      </c>
-      <c r="R11" s="44"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="56">
-        <v>1</v>
-      </c>
-      <c r="U11" s="51">
-        <v>1</v>
-      </c>
-      <c r="V11" s="44">
-        <v>1</v>
-      </c>
-      <c r="W11" s="12"/>
-      <c r="X11" s="56"/>
-      <c r="Y11" s="51"/>
-      <c r="Z11" s="44"/>
+      <c r="P11" s="54">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="42">
+        <v>1</v>
+      </c>
+      <c r="S11" s="12">
+        <v>1</v>
+      </c>
+      <c r="T11" s="54">
+        <v>1</v>
+      </c>
+      <c r="U11" s="49"/>
+      <c r="V11" s="42">
+        <v>1</v>
+      </c>
+      <c r="W11" s="12">
+        <v>1</v>
+      </c>
+      <c r="X11" s="54">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="42"/>
       <c r="AA11" s="12"/>
-      <c r="AB11" s="56">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="51"/>
-      <c r="AD11" s="44">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="56">
-        <v>1</v>
-      </c>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="42"/>
+      <c r="AE11" s="12"/>
+      <c r="AF11" s="54"/>
       <c r="AG11" s="13">
-        <f t="shared" si="0"/>
+        <f>SUM(E11:AF11)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14">
-        <v>9</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="9" t="s">
+    <row r="12" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="49">
+        <f>SUM(E4:E11)</f>
+        <v>5</v>
+      </c>
+      <c r="F12" s="42">
+        <f t="shared" ref="F12:AG12" si="1">SUM(F4:F11)</f>
         <v>4</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="56">
-        <v>1</v>
-      </c>
-      <c r="I12" s="51"/>
-      <c r="J12" s="44">
-        <v>1</v>
-      </c>
-      <c r="K12" s="12">
-        <v>1</v>
-      </c>
-      <c r="L12" s="56">
-        <v>1</v>
-      </c>
-      <c r="M12" s="51">
-        <v>1</v>
-      </c>
-      <c r="N12" s="44">
-        <v>1</v>
-      </c>
-      <c r="O12" s="12">
-        <v>1</v>
-      </c>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="44">
-        <v>1</v>
-      </c>
-      <c r="S12" s="12"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="44">
-        <v>1</v>
-      </c>
-      <c r="W12" s="12"/>
-      <c r="X12" s="56">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="44">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="56"/>
-      <c r="AC12" s="51"/>
-      <c r="AD12" s="44"/>
-      <c r="AE12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="56">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="13">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14">
-        <v>10</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="51">
-        <v>1</v>
-      </c>
-      <c r="F13" s="44"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="51">
-        <v>1</v>
-      </c>
-      <c r="J13" s="44">
-        <v>1</v>
-      </c>
-      <c r="K13" s="12">
-        <v>1</v>
-      </c>
-      <c r="L13" s="56">
-        <v>1</v>
-      </c>
-      <c r="M13" s="51"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="12">
-        <v>1</v>
-      </c>
-      <c r="P13" s="56">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="44">
-        <v>1</v>
-      </c>
-      <c r="S13" s="12">
-        <v>1</v>
-      </c>
-      <c r="T13" s="56">
-        <v>1</v>
-      </c>
-      <c r="U13" s="51"/>
-      <c r="V13" s="44">
-        <v>1</v>
-      </c>
-      <c r="W13" s="12">
-        <v>1</v>
-      </c>
-      <c r="X13" s="56">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="44"/>
-      <c r="AA13" s="12"/>
-      <c r="AB13" s="56"/>
-      <c r="AC13" s="51"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="12"/>
-      <c r="AF13" s="56"/>
-      <c r="AG13" s="13">
-        <f>SUM(E13:AF13)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="51">
-        <f>SUM(E6:E13)</f>
-        <v>5</v>
-      </c>
-      <c r="F14" s="44">
-        <f t="shared" ref="F14:AG14" si="1">SUM(F6:F13)</f>
-        <v>4</v>
-      </c>
-      <c r="G14" s="12">
+      <c r="G12" s="12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H14" s="56">
+      <c r="H12" s="54">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I12" s="49">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J14" s="44">
+      <c r="J12" s="42">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K12" s="12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L14" s="56">
+      <c r="L12" s="54">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="M14" s="51">
+      <c r="M12" s="49">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N14" s="44">
+      <c r="N12" s="42">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O12" s="12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="P14" s="56">
+      <c r="P12" s="54">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="Q14" s="51">
+      <c r="Q12" s="49">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="R14" s="44">
+      <c r="R12" s="42">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S12" s="12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="T14" s="56">
+      <c r="T12" s="54">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U14" s="51">
+      <c r="U12" s="49">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="V14" s="44">
+      <c r="V12" s="42">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="W14" s="12">
+      <c r="W12" s="12">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="X14" s="56">
+      <c r="X12" s="54">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="Y14" s="51">
+      <c r="Y12" s="49">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="Z14" s="44">
+      <c r="Z12" s="42">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="AA14" s="12">
+      <c r="AA12" s="12">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="AB14" s="56">
+      <c r="AB12" s="54">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AC14" s="51">
+      <c r="AC12" s="49">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AD14" s="44">
+      <c r="AD12" s="42">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AE14" s="12">
+      <c r="AE12" s="12">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="AF14" s="56">
+      <c r="AF12" s="54">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="AG14" s="11">
+      <c r="AG12" s="11">
         <f t="shared" si="1"/>
         <v>112</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C13" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:C13">
-      <sortCondition ref="C2:C13"/>
+  <autoFilter ref="A2:C11" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C11">
+      <sortCondition ref="C2:C11"/>
     </sortState>
   </autoFilter>
   <mergeCells count="13">
@@ -2860,200 +2705,200 @@
     <col min="1" max="1" width="4.1640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.83203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18" style="30" customWidth="1"/>
+    <col min="4" max="4" width="18" style="28" customWidth="1"/>
     <col min="5" max="32" width="5.83203125" style="8" customWidth="1"/>
     <col min="33" max="36" width="8.83203125" style="2"/>
     <col min="37" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="74"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="73"/>
     </row>
     <row r="2" spans="1:35" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="71">
+      <c r="E2" s="70">
         <v>46180</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71">
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70">
         <v>46181</v>
       </c>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71">
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70">
         <v>46182</v>
       </c>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71">
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70">
         <v>46183</v>
       </c>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71">
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70">
         <v>46184</v>
       </c>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71">
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
+      <c r="Y2" s="70">
         <v>46187</v>
       </c>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71">
+      <c r="Z2" s="70"/>
+      <c r="AA2" s="70"/>
+      <c r="AB2" s="70"/>
+      <c r="AC2" s="70">
         <v>46188</v>
       </c>
-      <c r="AD2" s="71"/>
-      <c r="AE2" s="71"/>
-      <c r="AF2" s="71"/>
-      <c r="AG2" s="72" t="s">
+      <c r="AD2" s="70"/>
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="71" t="s">
         <v>63</v>
       </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
     </row>
     <row r="3" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="32">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="F3" s="7">
         <v>11</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="30">
         <v>12.3</v>
       </c>
       <c r="H3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="J3" s="7">
         <v>11</v>
       </c>
-      <c r="K3" s="32">
+      <c r="K3" s="30">
         <v>12.3</v>
       </c>
       <c r="L3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M3" s="32">
+      <c r="M3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="N3" s="7">
         <v>11</v>
       </c>
-      <c r="O3" s="32">
+      <c r="O3" s="30">
         <v>12.3</v>
       </c>
       <c r="P3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Q3" s="32">
+      <c r="Q3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="R3" s="7">
         <v>11</v>
       </c>
-      <c r="S3" s="32">
+      <c r="S3" s="30">
         <v>12.3</v>
       </c>
       <c r="T3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="U3" s="32">
+      <c r="U3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="V3" s="7">
         <v>11</v>
       </c>
-      <c r="W3" s="32">
+      <c r="W3" s="30">
         <v>12.3</v>
       </c>
       <c r="X3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Y3" s="32">
+      <c r="Y3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="Z3" s="7">
         <v>11</v>
       </c>
-      <c r="AA3" s="32">
+      <c r="AA3" s="30">
         <v>12.3</v>
       </c>
       <c r="AB3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AC3" s="32">
+      <c r="AC3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="AD3" s="7">
         <v>11</v>
       </c>
-      <c r="AE3" s="32">
+      <c r="AE3" s="30">
         <v>12.3</v>
       </c>
       <c r="AF3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AG3" s="72"/>
+      <c r="AG3" s="71"/>
     </row>
     <row r="4" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
@@ -3068,51 +2913,51 @@
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="31">
         <v>1</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="33">
+      <c r="G4" s="31">
         <v>1</v>
       </c>
       <c r="H4" s="11"/>
-      <c r="I4" s="33"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="11">
         <v>1</v>
       </c>
-      <c r="K4" s="33"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="11"/>
-      <c r="M4" s="33"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="11"/>
-      <c r="O4" s="33">
+      <c r="O4" s="31">
         <v>1</v>
       </c>
       <c r="P4" s="11"/>
-      <c r="Q4" s="33"/>
+      <c r="Q4" s="31"/>
       <c r="R4" s="11">
         <v>1</v>
       </c>
-      <c r="S4" s="33"/>
+      <c r="S4" s="31"/>
       <c r="T4" s="11"/>
-      <c r="U4" s="33">
+      <c r="U4" s="31">
         <v>1</v>
       </c>
       <c r="V4" s="11"/>
-      <c r="W4" s="33"/>
+      <c r="W4" s="31"/>
       <c r="X4" s="11"/>
-      <c r="Y4" s="33"/>
+      <c r="Y4" s="31"/>
       <c r="Z4" s="11">
         <v>1</v>
       </c>
-      <c r="AA4" s="33">
+      <c r="AA4" s="31">
         <v>1</v>
       </c>
       <c r="AB4" s="11"/>
-      <c r="AC4" s="33"/>
+      <c r="AC4" s="31"/>
       <c r="AD4" s="11">
         <v>1</v>
       </c>
-      <c r="AE4" s="33">
+      <c r="AE4" s="31">
         <v>1</v>
       </c>
       <c r="AF4" s="11"/>
@@ -3134,39 +2979,39 @@
       <c r="D5" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="34"/>
+      <c r="E5" s="32"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="34"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="11"/>
-      <c r="I5" s="34"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="11">
         <v>1</v>
       </c>
-      <c r="K5" s="34"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="11">
         <v>1</v>
       </c>
-      <c r="M5" s="34"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="11"/>
-      <c r="O5" s="34"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="11"/>
-      <c r="Q5" s="34"/>
+      <c r="Q5" s="32"/>
       <c r="R5" s="11"/>
-      <c r="S5" s="34"/>
+      <c r="S5" s="32"/>
       <c r="T5" s="11"/>
-      <c r="U5" s="34"/>
+      <c r="U5" s="32"/>
       <c r="V5" s="11"/>
-      <c r="W5" s="34"/>
+      <c r="W5" s="32"/>
       <c r="X5" s="11"/>
-      <c r="Y5" s="34"/>
+      <c r="Y5" s="32"/>
       <c r="Z5" s="11"/>
-      <c r="AA5" s="34"/>
+      <c r="AA5" s="32"/>
       <c r="AB5" s="11"/>
-      <c r="AC5" s="34"/>
+      <c r="AC5" s="32"/>
       <c r="AD5" s="11">
         <v>1</v>
       </c>
-      <c r="AE5" s="34">
+      <c r="AE5" s="32">
         <v>1</v>
       </c>
       <c r="AF5" s="11"/>
@@ -3188,47 +3033,47 @@
       <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="34"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="34"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="11"/>
-      <c r="I6" s="34"/>
+      <c r="I6" s="32"/>
       <c r="J6" s="11">
         <v>1</v>
       </c>
-      <c r="K6" s="34"/>
+      <c r="K6" s="32"/>
       <c r="L6" s="11">
         <v>1</v>
       </c>
-      <c r="M6" s="34"/>
+      <c r="M6" s="32"/>
       <c r="N6" s="11"/>
-      <c r="O6" s="34"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="11">
         <v>1</v>
       </c>
-      <c r="Q6" s="34"/>
+      <c r="Q6" s="32"/>
       <c r="R6" s="11"/>
-      <c r="S6" s="34"/>
+      <c r="S6" s="32"/>
       <c r="T6" s="11">
         <v>1</v>
       </c>
-      <c r="U6" s="34"/>
+      <c r="U6" s="32"/>
       <c r="V6" s="11"/>
-      <c r="W6" s="34"/>
+      <c r="W6" s="32"/>
       <c r="X6" s="11">
         <v>1</v>
       </c>
-      <c r="Y6" s="34"/>
+      <c r="Y6" s="32"/>
       <c r="Z6" s="11">
         <v>1</v>
       </c>
-      <c r="AA6" s="34">
+      <c r="AA6" s="32">
         <v>1</v>
       </c>
       <c r="AB6" s="11"/>
-      <c r="AC6" s="34"/>
+      <c r="AC6" s="32"/>
       <c r="AD6" s="11"/>
-      <c r="AE6" s="34">
+      <c r="AE6" s="32">
         <v>1</v>
       </c>
       <c r="AF6" s="11"/>
@@ -3250,43 +3095,43 @@
       <c r="D7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="31">
         <v>1</v>
       </c>
       <c r="F7" s="11"/>
-      <c r="G7" s="33"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="11"/>
-      <c r="I7" s="33"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="11">
         <v>1</v>
       </c>
-      <c r="K7" s="33"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="11">
         <v>1</v>
       </c>
-      <c r="M7" s="33"/>
+      <c r="M7" s="31"/>
       <c r="N7" s="11"/>
-      <c r="O7" s="33"/>
+      <c r="O7" s="31"/>
       <c r="P7" s="11"/>
-      <c r="Q7" s="33"/>
+      <c r="Q7" s="31"/>
       <c r="R7" s="11"/>
-      <c r="S7" s="33"/>
+      <c r="S7" s="31"/>
       <c r="T7" s="11"/>
-      <c r="U7" s="33"/>
+      <c r="U7" s="31"/>
       <c r="V7" s="11"/>
-      <c r="W7" s="33"/>
+      <c r="W7" s="31"/>
       <c r="X7" s="11"/>
-      <c r="Y7" s="33"/>
+      <c r="Y7" s="31"/>
       <c r="Z7" s="11">
         <v>1</v>
       </c>
-      <c r="AA7" s="33">
+      <c r="AA7" s="31">
         <v>1</v>
       </c>
       <c r="AB7" s="11"/>
-      <c r="AC7" s="33"/>
+      <c r="AC7" s="31"/>
       <c r="AD7" s="11"/>
-      <c r="AE7" s="33">
+      <c r="AE7" s="31">
         <v>1</v>
       </c>
       <c r="AF7" s="11"/>
@@ -3308,43 +3153,43 @@
       <c r="D8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="31">
         <v>1</v>
       </c>
       <c r="F8" s="11"/>
-      <c r="G8" s="33"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="11"/>
-      <c r="I8" s="33"/>
+      <c r="I8" s="31"/>
       <c r="J8" s="11">
         <v>1</v>
       </c>
-      <c r="K8" s="33"/>
+      <c r="K8" s="31"/>
       <c r="L8" s="11"/>
-      <c r="M8" s="33"/>
+      <c r="M8" s="31"/>
       <c r="N8" s="11"/>
-      <c r="O8" s="33"/>
+      <c r="O8" s="31"/>
       <c r="P8" s="11"/>
-      <c r="Q8" s="33"/>
+      <c r="Q8" s="31"/>
       <c r="R8" s="11"/>
-      <c r="S8" s="33"/>
+      <c r="S8" s="31"/>
       <c r="T8" s="11"/>
-      <c r="U8" s="33"/>
+      <c r="U8" s="31"/>
       <c r="V8" s="11"/>
-      <c r="W8" s="33"/>
+      <c r="W8" s="31"/>
       <c r="X8" s="11"/>
-      <c r="Y8" s="33">
+      <c r="Y8" s="31">
         <v>1</v>
       </c>
       <c r="Z8" s="11">
         <v>1</v>
       </c>
-      <c r="AA8" s="33">
+      <c r="AA8" s="31">
         <v>1</v>
       </c>
       <c r="AB8" s="11"/>
-      <c r="AC8" s="33"/>
+      <c r="AC8" s="31"/>
       <c r="AD8" s="11"/>
-      <c r="AE8" s="33">
+      <c r="AE8" s="31">
         <v>1</v>
       </c>
       <c r="AF8" s="11"/>
@@ -3366,39 +3211,39 @@
       <c r="D9" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="33"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="33"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="33"/>
+      <c r="I9" s="31"/>
       <c r="J9" s="11"/>
-      <c r="K9" s="33"/>
+      <c r="K9" s="31"/>
       <c r="L9" s="11"/>
-      <c r="M9" s="33"/>
+      <c r="M9" s="31"/>
       <c r="N9" s="11"/>
-      <c r="O9" s="33"/>
+      <c r="O9" s="31"/>
       <c r="P9" s="11"/>
-      <c r="Q9" s="33"/>
+      <c r="Q9" s="31"/>
       <c r="R9" s="11"/>
-      <c r="S9" s="33"/>
+      <c r="S9" s="31"/>
       <c r="T9" s="11"/>
-      <c r="U9" s="33">
+      <c r="U9" s="31">
         <v>1</v>
       </c>
       <c r="V9" s="11"/>
-      <c r="W9" s="33"/>
+      <c r="W9" s="31"/>
       <c r="X9" s="11"/>
-      <c r="Y9" s="33"/>
+      <c r="Y9" s="31"/>
       <c r="Z9" s="11">
         <v>1</v>
       </c>
-      <c r="AA9" s="33">
+      <c r="AA9" s="31">
         <v>1</v>
       </c>
       <c r="AB9" s="11"/>
-      <c r="AC9" s="33"/>
+      <c r="AC9" s="31"/>
       <c r="AD9" s="11"/>
-      <c r="AE9" s="33"/>
+      <c r="AE9" s="31"/>
       <c r="AF9" s="11"/>
       <c r="AG9" s="13">
         <f t="shared" si="0"/>
@@ -3418,49 +3263,49 @@
       <c r="D10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="34"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="11">
         <v>1</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="32">
         <v>1</v>
       </c>
       <c r="H10" s="11"/>
-      <c r="I10" s="34"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="11"/>
-      <c r="K10" s="34">
+      <c r="K10" s="32">
         <v>1</v>
       </c>
       <c r="L10" s="11">
         <v>1</v>
       </c>
-      <c r="M10" s="34"/>
+      <c r="M10" s="32"/>
       <c r="N10" s="11">
         <v>1</v>
       </c>
-      <c r="O10" s="34"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="11"/>
-      <c r="Q10" s="34"/>
+      <c r="Q10" s="32"/>
       <c r="R10" s="11"/>
-      <c r="S10" s="34">
+      <c r="S10" s="32">
         <v>1</v>
       </c>
       <c r="T10" s="11"/>
-      <c r="U10" s="34"/>
+      <c r="U10" s="32"/>
       <c r="V10" s="11"/>
-      <c r="W10" s="34"/>
+      <c r="W10" s="32"/>
       <c r="X10" s="11"/>
-      <c r="Y10" s="34"/>
+      <c r="Y10" s="32"/>
       <c r="Z10" s="11">
         <v>1</v>
       </c>
-      <c r="AA10" s="34">
+      <c r="AA10" s="32">
         <v>1</v>
       </c>
       <c r="AB10" s="11"/>
-      <c r="AC10" s="34"/>
+      <c r="AC10" s="32"/>
       <c r="AD10" s="11"/>
-      <c r="AE10" s="34">
+      <c r="AE10" s="32">
         <v>1</v>
       </c>
       <c r="AF10" s="11"/>
@@ -3482,53 +3327,53 @@
       <c r="D11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="31">
         <v>1</v>
       </c>
       <c r="F11" s="11">
         <v>1</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="31">
         <v>1</v>
       </c>
       <c r="H11" s="11"/>
-      <c r="I11" s="33">
+      <c r="I11" s="31">
         <v>1</v>
       </c>
       <c r="J11" s="11">
         <v>1</v>
       </c>
-      <c r="K11" s="33"/>
+      <c r="K11" s="31"/>
       <c r="L11" s="11"/>
-      <c r="M11" s="33">
+      <c r="M11" s="31">
         <v>1</v>
       </c>
       <c r="N11" s="11"/>
-      <c r="O11" s="33">
+      <c r="O11" s="31">
         <v>1</v>
       </c>
       <c r="P11" s="11"/>
-      <c r="Q11" s="33"/>
+      <c r="Q11" s="31"/>
       <c r="R11" s="11"/>
-      <c r="S11" s="33">
+      <c r="S11" s="31">
         <v>1</v>
       </c>
       <c r="T11" s="11"/>
-      <c r="U11" s="33"/>
+      <c r="U11" s="31"/>
       <c r="V11" s="11"/>
-      <c r="W11" s="33">
+      <c r="W11" s="31">
         <v>1</v>
       </c>
       <c r="X11" s="11"/>
-      <c r="Y11" s="33"/>
+      <c r="Y11" s="31"/>
       <c r="Z11" s="11"/>
-      <c r="AA11" s="33">
+      <c r="AA11" s="31">
         <v>1</v>
       </c>
       <c r="AB11" s="11"/>
-      <c r="AC11" s="33"/>
+      <c r="AC11" s="31"/>
       <c r="AD11" s="11"/>
-      <c r="AE11" s="33"/>
+      <c r="AE11" s="31"/>
       <c r="AF11" s="11"/>
       <c r="AG11" s="13">
         <f t="shared" si="0"/>
@@ -3548,53 +3393,53 @@
       <c r="D12" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="31">
         <v>1</v>
       </c>
       <c r="F12" s="11">
         <v>1</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="31">
         <v>1</v>
       </c>
       <c r="H12" s="11"/>
-      <c r="I12" s="33"/>
+      <c r="I12" s="31"/>
       <c r="J12" s="11">
         <v>1</v>
       </c>
-      <c r="K12" s="33"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="11">
         <v>1</v>
       </c>
-      <c r="M12" s="33"/>
+      <c r="M12" s="31"/>
       <c r="N12" s="11"/>
-      <c r="O12" s="33"/>
+      <c r="O12" s="31"/>
       <c r="P12" s="11"/>
-      <c r="Q12" s="33">
+      <c r="Q12" s="31">
         <v>1</v>
       </c>
       <c r="R12" s="11"/>
-      <c r="S12" s="33">
+      <c r="S12" s="31">
         <v>1</v>
       </c>
       <c r="T12" s="11"/>
-      <c r="U12" s="33">
+      <c r="U12" s="31">
         <v>1</v>
       </c>
       <c r="V12" s="11"/>
-      <c r="W12" s="33">
+      <c r="W12" s="31">
         <v>1</v>
       </c>
       <c r="X12" s="11"/>
-      <c r="Y12" s="33"/>
+      <c r="Y12" s="31"/>
       <c r="Z12" s="11"/>
-      <c r="AA12" s="33">
+      <c r="AA12" s="31">
         <v>1</v>
       </c>
       <c r="AB12" s="11"/>
-      <c r="AC12" s="33"/>
+      <c r="AC12" s="31"/>
       <c r="AD12" s="11"/>
-      <c r="AE12" s="33"/>
+      <c r="AE12" s="31"/>
       <c r="AF12" s="11"/>
       <c r="AG12" s="13">
         <f t="shared" si="0"/>
@@ -3614,47 +3459,47 @@
       <c r="D13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="33"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="33"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="11">
         <v>1</v>
       </c>
-      <c r="I13" s="33"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="11"/>
-      <c r="K13" s="33"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="11">
         <v>1</v>
       </c>
-      <c r="M13" s="33"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="11"/>
-      <c r="O13" s="33"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="11">
         <v>1</v>
       </c>
-      <c r="Q13" s="33"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="11"/>
-      <c r="S13" s="33"/>
+      <c r="S13" s="31"/>
       <c r="T13" s="11">
         <v>1</v>
       </c>
-      <c r="U13" s="33"/>
+      <c r="U13" s="31"/>
       <c r="V13" s="11"/>
-      <c r="W13" s="33"/>
+      <c r="W13" s="31"/>
       <c r="X13" s="11">
         <v>1</v>
       </c>
-      <c r="Y13" s="33"/>
+      <c r="Y13" s="31"/>
       <c r="Z13" s="11"/>
-      <c r="AA13" s="33">
+      <c r="AA13" s="31">
         <v>1</v>
       </c>
       <c r="AB13" s="11">
         <v>1</v>
       </c>
-      <c r="AC13" s="33"/>
+      <c r="AC13" s="31"/>
       <c r="AD13" s="11"/>
-      <c r="AE13" s="33">
+      <c r="AE13" s="31">
         <v>1</v>
       </c>
       <c r="AF13" s="11"/>
@@ -3676,45 +3521,45 @@
       <c r="D14" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="33"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="33">
+      <c r="G14" s="31">
         <v>1</v>
       </c>
       <c r="H14" s="11">
         <v>1</v>
       </c>
-      <c r="I14" s="33"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="11">
         <v>1</v>
       </c>
-      <c r="K14" s="33"/>
+      <c r="K14" s="31"/>
       <c r="L14" s="11">
         <v>1</v>
       </c>
-      <c r="M14" s="33"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="11"/>
-      <c r="O14" s="33">
+      <c r="O14" s="31">
         <v>1</v>
       </c>
       <c r="P14" s="11"/>
-      <c r="Q14" s="33"/>
+      <c r="Q14" s="31"/>
       <c r="R14" s="11"/>
-      <c r="S14" s="33"/>
+      <c r="S14" s="31"/>
       <c r="T14" s="11"/>
-      <c r="U14" s="33"/>
+      <c r="U14" s="31"/>
       <c r="V14" s="11"/>
-      <c r="W14" s="33"/>
+      <c r="W14" s="31"/>
       <c r="X14" s="11"/>
-      <c r="Y14" s="33"/>
+      <c r="Y14" s="31"/>
       <c r="Z14" s="11"/>
-      <c r="AA14" s="33"/>
+      <c r="AA14" s="31"/>
       <c r="AB14" s="11">
         <v>1</v>
       </c>
-      <c r="AC14" s="33"/>
+      <c r="AC14" s="31"/>
       <c r="AD14" s="11"/>
-      <c r="AE14" s="33"/>
+      <c r="AE14" s="31"/>
       <c r="AF14" s="11">
         <v>1</v>
       </c>
@@ -3736,47 +3581,47 @@
       <c r="D15" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="35">
+      <c r="G15" s="33">
         <v>1</v>
       </c>
       <c r="H15" s="11">
         <v>1</v>
       </c>
-      <c r="I15" s="35"/>
+      <c r="I15" s="33"/>
       <c r="J15" s="11">
         <v>1</v>
       </c>
-      <c r="K15" s="35"/>
+      <c r="K15" s="33"/>
       <c r="L15" s="11">
         <v>1</v>
       </c>
-      <c r="M15" s="35"/>
+      <c r="M15" s="33"/>
       <c r="N15" s="11"/>
-      <c r="O15" s="35"/>
+      <c r="O15" s="33"/>
       <c r="P15" s="11">
         <v>1</v>
       </c>
-      <c r="Q15" s="35"/>
+      <c r="Q15" s="33"/>
       <c r="R15" s="11"/>
-      <c r="S15" s="35"/>
+      <c r="S15" s="33"/>
       <c r="T15" s="11">
         <v>1</v>
       </c>
-      <c r="U15" s="35"/>
+      <c r="U15" s="33"/>
       <c r="V15" s="11"/>
-      <c r="W15" s="35"/>
+      <c r="W15" s="33"/>
       <c r="X15" s="11"/>
-      <c r="Y15" s="35"/>
+      <c r="Y15" s="33"/>
       <c r="Z15" s="11"/>
-      <c r="AA15" s="35"/>
+      <c r="AA15" s="33"/>
       <c r="AB15" s="11">
         <v>1</v>
       </c>
-      <c r="AC15" s="35"/>
+      <c r="AC15" s="33"/>
       <c r="AD15" s="11"/>
-      <c r="AE15" s="35"/>
+      <c r="AE15" s="33"/>
       <c r="AF15" s="11">
         <v>1</v>
       </c>
@@ -3798,41 +3643,41 @@
       <c r="D16" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="35"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="35"/>
+      <c r="G16" s="33"/>
       <c r="H16" s="11">
         <v>1</v>
       </c>
-      <c r="I16" s="35"/>
+      <c r="I16" s="33"/>
       <c r="J16" s="11"/>
-      <c r="K16" s="35"/>
+      <c r="K16" s="33"/>
       <c r="L16" s="11">
         <v>1</v>
       </c>
-      <c r="M16" s="35"/>
+      <c r="M16" s="33"/>
       <c r="N16" s="11"/>
-      <c r="O16" s="35"/>
+      <c r="O16" s="33"/>
       <c r="P16" s="11">
         <v>1</v>
       </c>
-      <c r="Q16" s="35"/>
+      <c r="Q16" s="33"/>
       <c r="R16" s="11"/>
-      <c r="S16" s="35"/>
+      <c r="S16" s="33"/>
       <c r="T16" s="11">
         <v>1</v>
       </c>
-      <c r="U16" s="35"/>
+      <c r="U16" s="33"/>
       <c r="V16" s="11"/>
-      <c r="W16" s="35"/>
+      <c r="W16" s="33"/>
       <c r="X16" s="11"/>
-      <c r="Y16" s="35"/>
+      <c r="Y16" s="33"/>
       <c r="Z16" s="11"/>
-      <c r="AA16" s="35"/>
+      <c r="AA16" s="33"/>
       <c r="AB16" s="11"/>
-      <c r="AC16" s="35"/>
+      <c r="AC16" s="33"/>
       <c r="AD16" s="11"/>
-      <c r="AE16" s="35"/>
+      <c r="AE16" s="33"/>
       <c r="AF16" s="11"/>
       <c r="AG16" s="13">
         <f t="shared" si="0"/>
@@ -3852,51 +3697,51 @@
       <c r="D17" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="31">
         <v>1</v>
       </c>
       <c r="F17" s="11"/>
-      <c r="G17" s="33">
+      <c r="G17" s="31">
         <v>1</v>
       </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="33"/>
+      <c r="I17" s="31"/>
       <c r="J17" s="11">
         <v>1</v>
       </c>
-      <c r="K17" s="33">
+      <c r="K17" s="31">
         <v>1</v>
       </c>
       <c r="L17" s="11"/>
-      <c r="M17" s="33"/>
+      <c r="M17" s="31"/>
       <c r="N17" s="11">
         <v>1</v>
       </c>
-      <c r="O17" s="33">
+      <c r="O17" s="31">
         <v>1</v>
       </c>
       <c r="P17" s="11"/>
-      <c r="Q17" s="33"/>
+      <c r="Q17" s="31"/>
       <c r="R17" s="11"/>
-      <c r="S17" s="33">
+      <c r="S17" s="31">
         <v>1</v>
       </c>
       <c r="T17" s="11"/>
-      <c r="U17" s="33"/>
+      <c r="U17" s="31"/>
       <c r="V17" s="11"/>
-      <c r="W17" s="33">
+      <c r="W17" s="31">
         <v>1</v>
       </c>
       <c r="X17" s="11"/>
-      <c r="Y17" s="33"/>
+      <c r="Y17" s="31"/>
       <c r="Z17" s="11">
         <v>1</v>
       </c>
-      <c r="AA17" s="33"/>
+      <c r="AA17" s="31"/>
       <c r="AB17" s="11"/>
-      <c r="AC17" s="33"/>
+      <c r="AC17" s="31"/>
       <c r="AD17" s="11"/>
-      <c r="AE17" s="33"/>
+      <c r="AE17" s="31"/>
       <c r="AF17" s="11"/>
       <c r="AG17" s="13">
         <f t="shared" si="0"/>
@@ -3916,49 +3761,49 @@
       <c r="D18" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="31">
         <v>1</v>
       </c>
       <c r="F18" s="11">
         <v>1</v>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="31">
         <v>1</v>
       </c>
       <c r="H18" s="11">
         <v>1</v>
       </c>
-      <c r="I18" s="33"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="11">
         <v>1</v>
       </c>
-      <c r="K18" s="33"/>
+      <c r="K18" s="31"/>
       <c r="L18" s="11"/>
-      <c r="M18" s="33"/>
+      <c r="M18" s="31"/>
       <c r="N18" s="11"/>
-      <c r="O18" s="33">
+      <c r="O18" s="31">
         <v>1</v>
       </c>
       <c r="P18" s="11">
         <v>1</v>
       </c>
-      <c r="Q18" s="33"/>
+      <c r="Q18" s="31"/>
       <c r="R18" s="11"/>
-      <c r="S18" s="33"/>
+      <c r="S18" s="31"/>
       <c r="T18" s="11"/>
-      <c r="U18" s="33"/>
+      <c r="U18" s="31"/>
       <c r="V18" s="11"/>
-      <c r="W18" s="33"/>
+      <c r="W18" s="31"/>
       <c r="X18" s="11"/>
-      <c r="Y18" s="33"/>
+      <c r="Y18" s="31"/>
       <c r="Z18" s="11"/>
-      <c r="AA18" s="33"/>
+      <c r="AA18" s="31"/>
       <c r="AB18" s="11">
         <v>1</v>
       </c>
-      <c r="AC18" s="33"/>
+      <c r="AC18" s="31"/>
       <c r="AD18" s="11"/>
-      <c r="AE18" s="33"/>
+      <c r="AE18" s="31"/>
       <c r="AF18" s="11"/>
       <c r="AG18" s="13">
         <f t="shared" si="0"/>
@@ -3978,51 +3823,51 @@
       <c r="D19" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="31">
         <v>1</v>
       </c>
       <c r="F19" s="11"/>
-      <c r="G19" s="33"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="33"/>
+      <c r="I19" s="31"/>
       <c r="J19" s="11">
         <v>1</v>
       </c>
-      <c r="K19" s="33"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="11"/>
-      <c r="M19" s="33"/>
+      <c r="M19" s="31"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="33">
+      <c r="O19" s="31">
         <v>1</v>
       </c>
       <c r="P19" s="11">
         <v>1</v>
       </c>
-      <c r="Q19" s="33"/>
+      <c r="Q19" s="31"/>
       <c r="R19" s="11"/>
-      <c r="S19" s="33">
+      <c r="S19" s="31">
         <v>1</v>
       </c>
       <c r="T19" s="11">
         <v>1</v>
       </c>
-      <c r="U19" s="33"/>
+      <c r="U19" s="31"/>
       <c r="V19" s="11"/>
-      <c r="W19" s="33">
+      <c r="W19" s="31">
         <v>1</v>
       </c>
       <c r="X19" s="11">
         <v>1</v>
       </c>
-      <c r="Y19" s="33"/>
+      <c r="Y19" s="31"/>
       <c r="Z19" s="11"/>
-      <c r="AA19" s="33"/>
+      <c r="AA19" s="31"/>
       <c r="AB19" s="11">
         <v>1</v>
       </c>
-      <c r="AC19" s="33"/>
+      <c r="AC19" s="31"/>
       <c r="AD19" s="11"/>
-      <c r="AE19" s="33"/>
+      <c r="AE19" s="31"/>
       <c r="AF19" s="11">
         <v>1</v>
       </c>
@@ -4044,53 +3889,53 @@
       <c r="D20" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="31">
         <v>1</v>
       </c>
       <c r="F20" s="11"/>
-      <c r="G20" s="33">
+      <c r="G20" s="31">
         <v>1</v>
       </c>
       <c r="H20" s="11">
         <v>1</v>
       </c>
-      <c r="I20" s="33"/>
+      <c r="I20" s="31"/>
       <c r="J20" s="11">
         <v>1</v>
       </c>
-      <c r="K20" s="33"/>
+      <c r="K20" s="31"/>
       <c r="L20" s="11"/>
-      <c r="M20" s="33"/>
+      <c r="M20" s="31"/>
       <c r="N20" s="11"/>
-      <c r="O20" s="33">
+      <c r="O20" s="31">
         <v>1</v>
       </c>
       <c r="P20" s="11">
         <v>1</v>
       </c>
-      <c r="Q20" s="33"/>
+      <c r="Q20" s="31"/>
       <c r="R20" s="11"/>
-      <c r="S20" s="33">
+      <c r="S20" s="31">
         <v>1</v>
       </c>
       <c r="T20" s="11">
         <v>1</v>
       </c>
-      <c r="U20" s="33"/>
+      <c r="U20" s="31"/>
       <c r="V20" s="11"/>
-      <c r="W20" s="33">
+      <c r="W20" s="31">
         <v>1</v>
       </c>
       <c r="X20" s="11">
         <v>1</v>
       </c>
-      <c r="Y20" s="33"/>
+      <c r="Y20" s="31"/>
       <c r="Z20" s="11"/>
-      <c r="AA20" s="33"/>
+      <c r="AA20" s="31"/>
       <c r="AB20" s="11"/>
-      <c r="AC20" s="33"/>
+      <c r="AC20" s="31"/>
       <c r="AD20" s="11"/>
-      <c r="AE20" s="33"/>
+      <c r="AE20" s="31"/>
       <c r="AF20" s="11"/>
       <c r="AG20" s="13">
         <f t="shared" si="0"/>
@@ -4110,53 +3955,53 @@
       <c r="D21" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="31">
         <v>1</v>
       </c>
       <c r="F21" s="11"/>
-      <c r="G21" s="33">
+      <c r="G21" s="31">
         <v>1</v>
       </c>
       <c r="H21" s="11">
         <v>1</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="31">
         <v>1</v>
       </c>
       <c r="J21" s="11">
         <v>1</v>
       </c>
-      <c r="K21" s="33"/>
+      <c r="K21" s="31"/>
       <c r="L21" s="11"/>
-      <c r="M21" s="33"/>
+      <c r="M21" s="31"/>
       <c r="N21" s="11"/>
-      <c r="O21" s="33">
+      <c r="O21" s="31">
         <v>1</v>
       </c>
       <c r="P21" s="11"/>
-      <c r="Q21" s="33"/>
+      <c r="Q21" s="31"/>
       <c r="R21" s="11"/>
-      <c r="S21" s="33">
+      <c r="S21" s="31">
         <v>1</v>
       </c>
       <c r="T21" s="11"/>
-      <c r="U21" s="33">
+      <c r="U21" s="31">
         <v>1</v>
       </c>
       <c r="V21" s="11">
         <v>1</v>
       </c>
-      <c r="W21" s="33">
+      <c r="W21" s="31">
         <v>1</v>
       </c>
       <c r="X21" s="11"/>
-      <c r="Y21" s="33"/>
+      <c r="Y21" s="31"/>
       <c r="Z21" s="11"/>
-      <c r="AA21" s="33"/>
+      <c r="AA21" s="31"/>
       <c r="AB21" s="11"/>
-      <c r="AC21" s="33"/>
+      <c r="AC21" s="31"/>
       <c r="AD21" s="11"/>
-      <c r="AE21" s="33"/>
+      <c r="AE21" s="31"/>
       <c r="AF21" s="11"/>
       <c r="AG21" s="13">
         <f t="shared" si="0"/>
@@ -4176,47 +4021,47 @@
       <c r="D22" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="33"/>
+      <c r="E22" s="31"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="31"/>
       <c r="H22" s="11"/>
-      <c r="I22" s="33"/>
+      <c r="I22" s="31"/>
       <c r="J22" s="11"/>
-      <c r="K22" s="33"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="11"/>
-      <c r="M22" s="33"/>
+      <c r="M22" s="31"/>
       <c r="N22" s="11"/>
-      <c r="O22" s="33"/>
+      <c r="O22" s="31"/>
       <c r="P22" s="11"/>
-      <c r="Q22" s="33"/>
+      <c r="Q22" s="31"/>
       <c r="R22" s="11"/>
-      <c r="S22" s="33"/>
+      <c r="S22" s="31"/>
       <c r="T22" s="11"/>
-      <c r="U22" s="33">
+      <c r="U22" s="31">
         <v>1</v>
       </c>
       <c r="V22" s="11">
         <v>1</v>
       </c>
-      <c r="W22" s="33">
+      <c r="W22" s="31">
         <v>1</v>
       </c>
       <c r="X22" s="11">
         <v>1</v>
       </c>
-      <c r="Y22" s="33">
+      <c r="Y22" s="31">
         <v>1</v>
       </c>
       <c r="Z22" s="11"/>
-      <c r="AA22" s="33">
+      <c r="AA22" s="31">
         <v>1</v>
       </c>
       <c r="AB22" s="11">
         <v>1</v>
       </c>
-      <c r="AC22" s="33"/>
+      <c r="AC22" s="31"/>
       <c r="AD22" s="11"/>
-      <c r="AE22" s="33"/>
+      <c r="AE22" s="31"/>
       <c r="AF22" s="11">
         <v>1</v>
       </c>
@@ -4238,49 +4083,49 @@
       <c r="D23" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="33"/>
+      <c r="E23" s="31"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="31"/>
       <c r="H23" s="11"/>
-      <c r="I23" s="33"/>
+      <c r="I23" s="31"/>
       <c r="J23" s="11"/>
-      <c r="K23" s="33"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="11"/>
-      <c r="M23" s="33"/>
+      <c r="M23" s="31"/>
       <c r="N23" s="11"/>
-      <c r="O23" s="33"/>
+      <c r="O23" s="31"/>
       <c r="P23" s="11"/>
-      <c r="Q23" s="33"/>
+      <c r="Q23" s="31"/>
       <c r="R23" s="11"/>
-      <c r="S23" s="33"/>
+      <c r="S23" s="31"/>
       <c r="T23" s="11"/>
-      <c r="U23" s="33">
+      <c r="U23" s="31">
         <v>1</v>
       </c>
       <c r="V23" s="11">
         <v>1</v>
       </c>
-      <c r="W23" s="33">
+      <c r="W23" s="31">
         <v>1</v>
       </c>
       <c r="X23" s="11">
         <v>1</v>
       </c>
-      <c r="Y23" s="33">
+      <c r="Y23" s="31">
         <v>1</v>
       </c>
       <c r="Z23" s="11">
         <v>1</v>
       </c>
-      <c r="AA23" s="33">
+      <c r="AA23" s="31">
         <v>1</v>
       </c>
       <c r="AB23" s="11">
         <v>1</v>
       </c>
-      <c r="AC23" s="33"/>
+      <c r="AC23" s="31"/>
       <c r="AD23" s="11"/>
-      <c r="AE23" s="33"/>
+      <c r="AE23" s="31"/>
       <c r="AF23" s="11">
         <v>1</v>
       </c>
@@ -4302,47 +4147,47 @@
       <c r="D24" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="33"/>
+      <c r="E24" s="31"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="31"/>
       <c r="H24" s="11"/>
-      <c r="I24" s="33"/>
+      <c r="I24" s="31"/>
       <c r="J24" s="11"/>
-      <c r="K24" s="33"/>
+      <c r="K24" s="31"/>
       <c r="L24" s="11"/>
-      <c r="M24" s="33"/>
+      <c r="M24" s="31"/>
       <c r="N24" s="11"/>
-      <c r="O24" s="33"/>
+      <c r="O24" s="31"/>
       <c r="P24" s="11"/>
-      <c r="Q24" s="33"/>
+      <c r="Q24" s="31"/>
       <c r="R24" s="11"/>
-      <c r="S24" s="33"/>
+      <c r="S24" s="31"/>
       <c r="T24" s="11"/>
-      <c r="U24" s="33">
+      <c r="U24" s="31">
         <v>1</v>
       </c>
       <c r="V24" s="11">
         <v>1</v>
       </c>
-      <c r="W24" s="33">
+      <c r="W24" s="31">
         <v>1</v>
       </c>
       <c r="X24" s="11">
         <v>1</v>
       </c>
-      <c r="Y24" s="33">
+      <c r="Y24" s="31">
         <v>1</v>
       </c>
       <c r="Z24" s="11">
         <v>1</v>
       </c>
-      <c r="AA24" s="33"/>
+      <c r="AA24" s="31"/>
       <c r="AB24" s="11">
         <v>1</v>
       </c>
-      <c r="AC24" s="33"/>
+      <c r="AC24" s="31"/>
       <c r="AD24" s="11"/>
-      <c r="AE24" s="33"/>
+      <c r="AE24" s="31"/>
       <c r="AF24" s="11">
         <v>1</v>
       </c>
@@ -4364,47 +4209,47 @@
       <c r="D25" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="33"/>
+      <c r="E25" s="31"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="33"/>
+      <c r="G25" s="31"/>
       <c r="H25" s="11"/>
-      <c r="I25" s="33"/>
+      <c r="I25" s="31"/>
       <c r="J25" s="11"/>
-      <c r="K25" s="33"/>
+      <c r="K25" s="31"/>
       <c r="L25" s="11"/>
-      <c r="M25" s="33"/>
+      <c r="M25" s="31"/>
       <c r="N25" s="11"/>
-      <c r="O25" s="33"/>
+      <c r="O25" s="31"/>
       <c r="P25" s="11"/>
-      <c r="Q25" s="33"/>
+      <c r="Q25" s="31"/>
       <c r="R25" s="11"/>
-      <c r="S25" s="33"/>
+      <c r="S25" s="31"/>
       <c r="T25" s="11"/>
-      <c r="U25" s="33">
+      <c r="U25" s="31">
         <v>1</v>
       </c>
       <c r="V25" s="11">
         <v>1</v>
       </c>
-      <c r="W25" s="33"/>
+      <c r="W25" s="31"/>
       <c r="X25" s="11">
         <v>1</v>
       </c>
-      <c r="Y25" s="33">
+      <c r="Y25" s="31">
         <v>1</v>
       </c>
       <c r="Z25" s="11">
         <v>1</v>
       </c>
-      <c r="AA25" s="33">
+      <c r="AA25" s="31">
         <v>1</v>
       </c>
       <c r="AB25" s="11"/>
-      <c r="AC25" s="33">
+      <c r="AC25" s="31">
         <v>1</v>
       </c>
       <c r="AD25" s="11"/>
-      <c r="AE25" s="33"/>
+      <c r="AE25" s="31"/>
       <c r="AF25" s="11">
         <v>1</v>
       </c>
@@ -4426,47 +4271,47 @@
       <c r="D26" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="33"/>
+      <c r="E26" s="31"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="33"/>
+      <c r="G26" s="31"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="33"/>
+      <c r="I26" s="31"/>
       <c r="J26" s="11"/>
-      <c r="K26" s="33"/>
+      <c r="K26" s="31"/>
       <c r="L26" s="11"/>
-      <c r="M26" s="33"/>
+      <c r="M26" s="31"/>
       <c r="N26" s="11"/>
-      <c r="O26" s="33"/>
+      <c r="O26" s="31"/>
       <c r="P26" s="11"/>
-      <c r="Q26" s="33"/>
+      <c r="Q26" s="31"/>
       <c r="R26" s="11"/>
-      <c r="S26" s="33"/>
+      <c r="S26" s="31"/>
       <c r="T26" s="11"/>
-      <c r="U26" s="33">
+      <c r="U26" s="31">
         <v>1</v>
       </c>
       <c r="V26" s="11">
         <v>1</v>
       </c>
-      <c r="W26" s="33"/>
+      <c r="W26" s="31"/>
       <c r="X26" s="11">
         <v>1</v>
       </c>
-      <c r="Y26" s="33">
+      <c r="Y26" s="31">
         <v>1</v>
       </c>
       <c r="Z26" s="11">
         <v>1</v>
       </c>
-      <c r="AA26" s="33">
+      <c r="AA26" s="31">
         <v>1</v>
       </c>
       <c r="AB26" s="11"/>
-      <c r="AC26" s="33">
+      <c r="AC26" s="31">
         <v>1</v>
       </c>
       <c r="AD26" s="11"/>
-      <c r="AE26" s="33"/>
+      <c r="AE26" s="31"/>
       <c r="AF26" s="11"/>
       <c r="AG26" s="13">
         <f t="shared" si="0"/>
@@ -4486,37 +4331,37 @@
       <c r="D27" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="33"/>
+      <c r="E27" s="31"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="33"/>
+      <c r="G27" s="31"/>
       <c r="H27" s="11"/>
-      <c r="I27" s="33"/>
+      <c r="I27" s="31"/>
       <c r="J27" s="11"/>
-      <c r="K27" s="33"/>
+      <c r="K27" s="31"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="33"/>
+      <c r="M27" s="31"/>
       <c r="N27" s="11"/>
-      <c r="O27" s="33"/>
+      <c r="O27" s="31"/>
       <c r="P27" s="11"/>
-      <c r="Q27" s="33"/>
+      <c r="Q27" s="31"/>
       <c r="R27" s="11"/>
-      <c r="S27" s="33"/>
+      <c r="S27" s="31"/>
       <c r="T27" s="11"/>
-      <c r="U27" s="33"/>
+      <c r="U27" s="31"/>
       <c r="V27" s="11"/>
-      <c r="W27" s="33"/>
+      <c r="W27" s="31"/>
       <c r="X27" s="11">
         <v>1</v>
       </c>
-      <c r="Y27" s="33"/>
+      <c r="Y27" s="31"/>
       <c r="Z27" s="11"/>
-      <c r="AA27" s="33">
+      <c r="AA27" s="31">
         <v>1</v>
       </c>
       <c r="AB27" s="11"/>
-      <c r="AC27" s="33"/>
+      <c r="AC27" s="31"/>
       <c r="AD27" s="11"/>
-      <c r="AE27" s="33"/>
+      <c r="AE27" s="31"/>
       <c r="AF27" s="11"/>
       <c r="AG27" s="13">
         <f t="shared" si="0"/>
@@ -4536,53 +4381,53 @@
       <c r="D28" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="31">
         <v>1</v>
       </c>
       <c r="F28" s="11"/>
-      <c r="G28" s="33"/>
+      <c r="G28" s="31"/>
       <c r="H28" s="11"/>
-      <c r="I28" s="33">
+      <c r="I28" s="31">
         <v>1</v>
       </c>
       <c r="J28" s="11"/>
-      <c r="K28" s="33"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="11"/>
-      <c r="M28" s="33">
+      <c r="M28" s="31">
         <v>1</v>
       </c>
       <c r="N28" s="11"/>
-      <c r="O28" s="33">
+      <c r="O28" s="31">
         <v>1</v>
       </c>
       <c r="P28" s="11"/>
-      <c r="Q28" s="33">
+      <c r="Q28" s="31">
         <v>1</v>
       </c>
       <c r="R28" s="11"/>
-      <c r="S28" s="33">
+      <c r="S28" s="31">
         <v>1</v>
       </c>
       <c r="T28" s="11">
         <v>1</v>
       </c>
-      <c r="U28" s="33"/>
+      <c r="U28" s="31"/>
       <c r="V28" s="11"/>
-      <c r="W28" s="33">
+      <c r="W28" s="31">
         <v>1</v>
       </c>
       <c r="X28" s="11"/>
-      <c r="Y28" s="33"/>
+      <c r="Y28" s="31"/>
       <c r="Z28" s="11">
         <v>1</v>
       </c>
-      <c r="AA28" s="33">
+      <c r="AA28" s="31">
         <v>1</v>
       </c>
       <c r="AB28" s="11"/>
-      <c r="AC28" s="33"/>
+      <c r="AC28" s="31"/>
       <c r="AD28" s="11"/>
-      <c r="AE28" s="33"/>
+      <c r="AE28" s="31"/>
       <c r="AF28" s="11"/>
       <c r="AG28" s="13">
         <f t="shared" si="0"/>
@@ -4602,53 +4447,53 @@
       <c r="D29" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="31">
         <v>1</v>
       </c>
       <c r="F29" s="13"/>
-      <c r="G29" s="33">
+      <c r="G29" s="31">
         <v>1</v>
       </c>
       <c r="H29" s="13"/>
-      <c r="I29" s="33">
+      <c r="I29" s="31">
         <v>1</v>
       </c>
       <c r="J29" s="13"/>
-      <c r="K29" s="33">
+      <c r="K29" s="31">
         <v>1</v>
       </c>
       <c r="L29" s="13"/>
-      <c r="M29" s="33">
+      <c r="M29" s="31">
         <v>1</v>
       </c>
       <c r="N29" s="13"/>
-      <c r="O29" s="33">
+      <c r="O29" s="31">
         <v>1</v>
       </c>
       <c r="P29" s="13"/>
-      <c r="Q29" s="33">
+      <c r="Q29" s="31">
         <v>1</v>
       </c>
       <c r="R29" s="13">
         <v>1</v>
       </c>
-      <c r="S29" s="33">
+      <c r="S29" s="31">
         <v>1</v>
       </c>
       <c r="T29" s="13"/>
-      <c r="U29" s="33"/>
+      <c r="U29" s="31"/>
       <c r="V29" s="13"/>
-      <c r="W29" s="33">
+      <c r="W29" s="31">
         <v>1</v>
       </c>
       <c r="X29" s="13"/>
-      <c r="Y29" s="33"/>
+      <c r="Y29" s="31"/>
       <c r="Z29" s="13"/>
-      <c r="AA29" s="33"/>
+      <c r="AA29" s="31"/>
       <c r="AB29" s="13"/>
-      <c r="AC29" s="33"/>
+      <c r="AC29" s="31"/>
       <c r="AD29" s="13"/>
-      <c r="AE29" s="33"/>
+      <c r="AE29" s="31"/>
       <c r="AF29" s="13"/>
       <c r="AG29" s="13">
         <f t="shared" si="0"/>
@@ -4668,53 +4513,53 @@
       <c r="D30" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="33"/>
+      <c r="E30" s="31"/>
       <c r="F30" s="13"/>
-      <c r="G30" s="33"/>
+      <c r="G30" s="31"/>
       <c r="H30" s="13"/>
-      <c r="I30" s="33">
+      <c r="I30" s="31">
         <v>1</v>
       </c>
       <c r="J30" s="13"/>
-      <c r="K30" s="33"/>
+      <c r="K30" s="31"/>
       <c r="L30" s="13"/>
-      <c r="M30" s="33">
+      <c r="M30" s="31">
         <v>1</v>
       </c>
       <c r="N30" s="13"/>
-      <c r="O30" s="33">
+      <c r="O30" s="31">
         <v>1</v>
       </c>
       <c r="P30" s="13"/>
-      <c r="Q30" s="33">
+      <c r="Q30" s="31">
         <v>1</v>
       </c>
       <c r="R30" s="13">
         <v>1</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="31">
         <v>1</v>
       </c>
       <c r="T30" s="13"/>
-      <c r="U30" s="33">
+      <c r="U30" s="31">
         <v>1</v>
       </c>
       <c r="V30" s="13"/>
-      <c r="W30" s="33">
+      <c r="W30" s="31">
         <v>1</v>
       </c>
       <c r="X30" s="13"/>
-      <c r="Y30" s="33">
+      <c r="Y30" s="31">
         <v>1</v>
       </c>
       <c r="Z30" s="13"/>
-      <c r="AA30" s="33">
+      <c r="AA30" s="31">
         <v>1</v>
       </c>
       <c r="AB30" s="13"/>
-      <c r="AC30" s="33"/>
+      <c r="AC30" s="31"/>
       <c r="AD30" s="13"/>
-      <c r="AE30" s="33"/>
+      <c r="AE30" s="31"/>
       <c r="AF30" s="13"/>
       <c r="AG30" s="13">
         <f t="shared" si="0"/>
@@ -4734,53 +4579,53 @@
       <c r="D31" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="33"/>
+      <c r="E31" s="31"/>
       <c r="F31" s="13"/>
-      <c r="G31" s="33">
+      <c r="G31" s="31">
         <v>1</v>
       </c>
       <c r="H31" s="13"/>
-      <c r="I31" s="33">
+      <c r="I31" s="31">
         <v>1</v>
       </c>
       <c r="J31" s="13"/>
-      <c r="K31" s="33">
+      <c r="K31" s="31">
         <v>1</v>
       </c>
       <c r="L31" s="13"/>
-      <c r="M31" s="33">
+      <c r="M31" s="31">
         <v>1</v>
       </c>
       <c r="N31" s="13">
         <v>1</v>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="31">
         <v>1</v>
       </c>
       <c r="P31" s="13"/>
-      <c r="Q31" s="33">
+      <c r="Q31" s="31">
         <v>1</v>
       </c>
       <c r="R31" s="13">
         <v>1</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="31">
         <v>1</v>
       </c>
       <c r="T31" s="13"/>
-      <c r="U31" s="33"/>
+      <c r="U31" s="31"/>
       <c r="V31" s="13"/>
-      <c r="W31" s="33">
+      <c r="W31" s="31">
         <v>1</v>
       </c>
       <c r="X31" s="13"/>
-      <c r="Y31" s="33"/>
+      <c r="Y31" s="31"/>
       <c r="Z31" s="13"/>
-      <c r="AA31" s="33"/>
+      <c r="AA31" s="31"/>
       <c r="AB31" s="13"/>
-      <c r="AC31" s="33"/>
+      <c r="AC31" s="31"/>
       <c r="AD31" s="13"/>
-      <c r="AE31" s="33"/>
+      <c r="AE31" s="31"/>
       <c r="AF31" s="13"/>
       <c r="AG31" s="13">
         <f t="shared" si="0"/>
@@ -4800,53 +4645,53 @@
       <c r="D32" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="33"/>
+      <c r="E32" s="31"/>
       <c r="F32" s="13"/>
-      <c r="G32" s="33">
+      <c r="G32" s="31">
         <v>1</v>
       </c>
       <c r="H32" s="13"/>
-      <c r="I32" s="33">
+      <c r="I32" s="31">
         <v>1</v>
       </c>
       <c r="J32" s="13"/>
-      <c r="K32" s="33">
+      <c r="K32" s="31">
         <v>1</v>
       </c>
       <c r="L32" s="13"/>
-      <c r="M32" s="33">
+      <c r="M32" s="31">
         <v>1</v>
       </c>
       <c r="N32" s="13">
         <v>1</v>
       </c>
-      <c r="O32" s="33">
+      <c r="O32" s="31">
         <v>1</v>
       </c>
       <c r="P32" s="13"/>
-      <c r="Q32" s="33">
+      <c r="Q32" s="31">
         <v>1</v>
       </c>
       <c r="R32" s="13">
         <v>1</v>
       </c>
-      <c r="S32" s="33">
+      <c r="S32" s="31">
         <v>1</v>
       </c>
       <c r="T32" s="13"/>
-      <c r="U32" s="33"/>
+      <c r="U32" s="31"/>
       <c r="V32" s="13"/>
-      <c r="W32" s="33">
+      <c r="W32" s="31">
         <v>1</v>
       </c>
       <c r="X32" s="13"/>
-      <c r="Y32" s="33"/>
+      <c r="Y32" s="31"/>
       <c r="Z32" s="13"/>
-      <c r="AA32" s="33"/>
+      <c r="AA32" s="31"/>
       <c r="AB32" s="13"/>
-      <c r="AC32" s="33"/>
+      <c r="AC32" s="31"/>
       <c r="AD32" s="13"/>
-      <c r="AE32" s="33"/>
+      <c r="AE32" s="31"/>
       <c r="AF32" s="13"/>
       <c r="AG32" s="13">
         <f t="shared" si="0"/>
@@ -4866,53 +4711,53 @@
       <c r="D33" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="33"/>
+      <c r="E33" s="31"/>
       <c r="F33" s="11">
         <v>1</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="31"/>
       <c r="H33" s="11"/>
-      <c r="I33" s="33">
+      <c r="I33" s="31">
         <v>1</v>
       </c>
       <c r="J33" s="11"/>
-      <c r="K33" s="33">
+      <c r="K33" s="31">
         <v>1</v>
       </c>
       <c r="L33" s="11"/>
-      <c r="M33" s="33">
+      <c r="M33" s="31">
         <v>1</v>
       </c>
       <c r="N33" s="11">
         <v>1</v>
       </c>
-      <c r="O33" s="33"/>
+      <c r="O33" s="31"/>
       <c r="P33" s="11">
         <v>1</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="31">
         <v>1</v>
       </c>
       <c r="R33" s="11">
         <v>1</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="31">
         <v>1</v>
       </c>
       <c r="T33" s="11">
         <v>1</v>
       </c>
-      <c r="U33" s="33"/>
+      <c r="U33" s="31"/>
       <c r="V33" s="11"/>
-      <c r="W33" s="33"/>
+      <c r="W33" s="31"/>
       <c r="X33" s="11"/>
-      <c r="Y33" s="33"/>
+      <c r="Y33" s="31"/>
       <c r="Z33" s="11"/>
-      <c r="AA33" s="33"/>
+      <c r="AA33" s="31"/>
       <c r="AB33" s="11"/>
-      <c r="AC33" s="33"/>
+      <c r="AC33" s="31"/>
       <c r="AD33" s="11"/>
-      <c r="AE33" s="33"/>
+      <c r="AE33" s="31"/>
       <c r="AF33" s="11"/>
       <c r="AG33" s="13">
         <f t="shared" si="0"/>
@@ -4932,53 +4777,53 @@
       <c r="D34" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="33"/>
+      <c r="E34" s="31"/>
       <c r="F34" s="11">
         <v>1</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="31"/>
       <c r="H34" s="11">
         <v>1</v>
       </c>
-      <c r="I34" s="33">
+      <c r="I34" s="31">
         <v>1</v>
       </c>
       <c r="J34" s="11"/>
-      <c r="K34" s="33">
+      <c r="K34" s="31">
         <v>1</v>
       </c>
       <c r="L34" s="11"/>
-      <c r="M34" s="33">
+      <c r="M34" s="31">
         <v>1</v>
       </c>
       <c r="N34" s="11">
         <v>1</v>
       </c>
-      <c r="O34" s="33"/>
+      <c r="O34" s="31"/>
       <c r="P34" s="11"/>
-      <c r="Q34" s="33">
+      <c r="Q34" s="31">
         <v>1</v>
       </c>
       <c r="R34" s="11"/>
-      <c r="S34" s="33"/>
+      <c r="S34" s="31"/>
       <c r="T34" s="11">
         <v>1</v>
       </c>
-      <c r="U34" s="33"/>
+      <c r="U34" s="31"/>
       <c r="V34" s="11"/>
-      <c r="W34" s="33"/>
+      <c r="W34" s="31"/>
       <c r="X34" s="11">
         <v>1</v>
       </c>
-      <c r="Y34" s="33"/>
+      <c r="Y34" s="31"/>
       <c r="Z34" s="11"/>
-      <c r="AA34" s="33"/>
+      <c r="AA34" s="31"/>
       <c r="AB34" s="11"/>
-      <c r="AC34" s="33">
+      <c r="AC34" s="31">
         <v>1</v>
       </c>
       <c r="AD34" s="11"/>
-      <c r="AE34" s="33"/>
+      <c r="AE34" s="31"/>
       <c r="AF34" s="11"/>
       <c r="AG34" s="13">
         <f t="shared" si="0"/>
@@ -4998,53 +4843,53 @@
       <c r="D35" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E35" s="33"/>
+      <c r="E35" s="31"/>
       <c r="F35" s="11">
         <v>1</v>
       </c>
-      <c r="G35" s="33"/>
+      <c r="G35" s="31"/>
       <c r="H35" s="11">
         <v>1</v>
       </c>
-      <c r="I35" s="33">
+      <c r="I35" s="31">
         <v>1</v>
       </c>
       <c r="J35" s="11"/>
-      <c r="K35" s="33">
+      <c r="K35" s="31">
         <v>1</v>
       </c>
       <c r="L35" s="11"/>
-      <c r="M35" s="33">
+      <c r="M35" s="31">
         <v>1</v>
       </c>
       <c r="N35" s="11">
         <v>1</v>
       </c>
-      <c r="O35" s="33"/>
+      <c r="O35" s="31"/>
       <c r="P35" s="11"/>
-      <c r="Q35" s="33">
+      <c r="Q35" s="31">
         <v>1</v>
       </c>
       <c r="R35" s="11">
         <v>1</v>
       </c>
-      <c r="S35" s="33"/>
+      <c r="S35" s="31"/>
       <c r="T35" s="11"/>
-      <c r="U35" s="33">
+      <c r="U35" s="31">
         <v>1</v>
       </c>
       <c r="V35" s="11"/>
-      <c r="W35" s="33"/>
+      <c r="W35" s="31"/>
       <c r="X35" s="11">
         <v>1</v>
       </c>
-      <c r="Y35" s="33"/>
+      <c r="Y35" s="31"/>
       <c r="Z35" s="11"/>
-      <c r="AA35" s="33"/>
+      <c r="AA35" s="31"/>
       <c r="AB35" s="11"/>
-      <c r="AC35" s="33"/>
+      <c r="AC35" s="31"/>
       <c r="AD35" s="11"/>
-      <c r="AE35" s="33"/>
+      <c r="AE35" s="31"/>
       <c r="AF35" s="11"/>
       <c r="AG35" s="13">
         <f t="shared" si="0"/>
@@ -5064,119 +4909,119 @@
       <c r="D36" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="33"/>
+      <c r="E36" s="31"/>
       <c r="F36" s="11">
         <v>1</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="31"/>
       <c r="H36" s="11"/>
-      <c r="I36" s="33">
+      <c r="I36" s="31">
         <v>1</v>
       </c>
       <c r="J36" s="11"/>
-      <c r="K36" s="33">
+      <c r="K36" s="31">
         <v>1</v>
       </c>
       <c r="L36" s="11"/>
-      <c r="M36" s="33">
+      <c r="M36" s="31">
         <v>1</v>
       </c>
       <c r="N36" s="11">
         <v>1</v>
       </c>
-      <c r="O36" s="33"/>
+      <c r="O36" s="31"/>
       <c r="P36" s="11"/>
-      <c r="Q36" s="33">
+      <c r="Q36" s="31">
         <v>1</v>
       </c>
       <c r="R36" s="11">
         <v>1</v>
       </c>
-      <c r="S36" s="33"/>
+      <c r="S36" s="31"/>
       <c r="T36" s="11">
         <v>1</v>
       </c>
-      <c r="U36" s="33"/>
+      <c r="U36" s="31"/>
       <c r="V36" s="11"/>
-      <c r="W36" s="33"/>
+      <c r="W36" s="31"/>
       <c r="X36" s="11">
         <v>1</v>
       </c>
-      <c r="Y36" s="33"/>
+      <c r="Y36" s="31"/>
       <c r="Z36" s="11">
         <v>1</v>
       </c>
-      <c r="AA36" s="33"/>
+      <c r="AA36" s="31"/>
       <c r="AB36" s="11"/>
-      <c r="AC36" s="33"/>
+      <c r="AC36" s="31"/>
       <c r="AD36" s="11"/>
-      <c r="AE36" s="33"/>
+      <c r="AE36" s="31"/>
       <c r="AF36" s="11"/>
       <c r="AG36" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:33" s="39" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="36">
+    <row r="37" spans="1:33" s="37" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="34">
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E37" s="33"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="33">
-        <v>1</v>
-      </c>
-      <c r="L37" s="38"/>
-      <c r="M37" s="33">
-        <v>1</v>
-      </c>
-      <c r="N37" s="38">
-        <v>1</v>
-      </c>
-      <c r="O37" s="33"/>
-      <c r="P37" s="38"/>
-      <c r="Q37" s="33">
-        <v>1</v>
-      </c>
-      <c r="R37" s="38">
-        <v>1</v>
-      </c>
-      <c r="S37" s="33"/>
-      <c r="T37" s="38">
-        <v>1</v>
-      </c>
-      <c r="U37" s="33"/>
-      <c r="V37" s="38"/>
-      <c r="W37" s="33"/>
-      <c r="X37" s="38"/>
-      <c r="Y37" s="33">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="38">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="33"/>
-      <c r="AB37" s="38"/>
-      <c r="AC37" s="33">
-        <v>1</v>
-      </c>
-      <c r="AD37" s="38"/>
-      <c r="AE37" s="33"/>
-      <c r="AF37" s="38"/>
-      <c r="AG37" s="38">
+      <c r="E37" s="31"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="31">
+        <v>1</v>
+      </c>
+      <c r="L37" s="36"/>
+      <c r="M37" s="31">
+        <v>1</v>
+      </c>
+      <c r="N37" s="36">
+        <v>1</v>
+      </c>
+      <c r="O37" s="31"/>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="31">
+        <v>1</v>
+      </c>
+      <c r="R37" s="36">
+        <v>1</v>
+      </c>
+      <c r="S37" s="31"/>
+      <c r="T37" s="36">
+        <v>1</v>
+      </c>
+      <c r="U37" s="31"/>
+      <c r="V37" s="36"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="36"/>
+      <c r="Y37" s="31">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="36">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="31"/>
+      <c r="AB37" s="36"/>
+      <c r="AC37" s="31">
+        <v>1</v>
+      </c>
+      <c r="AD37" s="36"/>
+      <c r="AE37" s="31"/>
+      <c r="AF37" s="36"/>
+      <c r="AG37" s="36">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -5194,53 +5039,53 @@
       <c r="D38" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E38" s="33"/>
+      <c r="E38" s="31"/>
       <c r="F38" s="11">
         <v>1</v>
       </c>
-      <c r="G38" s="33"/>
+      <c r="G38" s="31"/>
       <c r="H38" s="11"/>
-      <c r="I38" s="33">
+      <c r="I38" s="31">
         <v>1</v>
       </c>
       <c r="J38" s="11"/>
-      <c r="K38" s="33">
+      <c r="K38" s="31">
         <v>1</v>
       </c>
       <c r="L38" s="11"/>
-      <c r="M38" s="33">
+      <c r="M38" s="31">
         <v>1</v>
       </c>
       <c r="N38" s="11">
         <v>1</v>
       </c>
-      <c r="O38" s="33"/>
+      <c r="O38" s="31"/>
       <c r="P38" s="11"/>
-      <c r="Q38" s="33">
+      <c r="Q38" s="31">
         <v>1</v>
       </c>
       <c r="R38" s="11">
         <v>1</v>
       </c>
-      <c r="S38" s="33"/>
+      <c r="S38" s="31"/>
       <c r="T38" s="11"/>
-      <c r="U38" s="33">
+      <c r="U38" s="31">
         <v>1</v>
       </c>
       <c r="V38" s="11">
         <v>1</v>
       </c>
-      <c r="W38" s="33"/>
+      <c r="W38" s="31"/>
       <c r="X38" s="11"/>
-      <c r="Y38" s="33">
+      <c r="Y38" s="31">
         <v>1</v>
       </c>
       <c r="Z38" s="11"/>
-      <c r="AA38" s="33"/>
+      <c r="AA38" s="31"/>
       <c r="AB38" s="11"/>
-      <c r="AC38" s="33"/>
+      <c r="AC38" s="31"/>
       <c r="AD38" s="11"/>
-      <c r="AE38" s="33"/>
+      <c r="AE38" s="31"/>
       <c r="AF38" s="11"/>
       <c r="AG38" s="13">
         <f t="shared" si="0"/>
@@ -5260,53 +5105,53 @@
       <c r="D39" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E39" s="33"/>
+      <c r="E39" s="31"/>
       <c r="F39" s="11">
         <v>1</v>
       </c>
-      <c r="G39" s="33"/>
+      <c r="G39" s="31"/>
       <c r="H39" s="11"/>
-      <c r="I39" s="33">
+      <c r="I39" s="31">
         <v>1</v>
       </c>
       <c r="J39" s="11"/>
-      <c r="K39" s="33">
+      <c r="K39" s="31">
         <v>1</v>
       </c>
       <c r="L39" s="11"/>
-      <c r="M39" s="33">
+      <c r="M39" s="31">
         <v>1</v>
       </c>
       <c r="N39" s="11">
         <v>1</v>
       </c>
-      <c r="O39" s="33"/>
+      <c r="O39" s="31"/>
       <c r="P39" s="11"/>
-      <c r="Q39" s="33">
+      <c r="Q39" s="31">
         <v>1</v>
       </c>
       <c r="R39" s="11">
         <v>1</v>
       </c>
-      <c r="S39" s="33"/>
+      <c r="S39" s="31"/>
       <c r="T39" s="11"/>
-      <c r="U39" s="33">
+      <c r="U39" s="31">
         <v>1</v>
       </c>
       <c r="V39" s="11">
         <v>1</v>
       </c>
-      <c r="W39" s="33"/>
+      <c r="W39" s="31"/>
       <c r="X39" s="11"/>
-      <c r="Y39" s="33"/>
+      <c r="Y39" s="31"/>
       <c r="Z39" s="11"/>
-      <c r="AA39" s="33"/>
+      <c r="AA39" s="31"/>
       <c r="AB39" s="11"/>
-      <c r="AC39" s="33">
+      <c r="AC39" s="31">
         <v>1</v>
       </c>
       <c r="AD39" s="11"/>
-      <c r="AE39" s="33"/>
+      <c r="AE39" s="31"/>
       <c r="AF39" s="11"/>
       <c r="AG39" s="13">
         <f t="shared" si="0"/>
@@ -5326,53 +5171,53 @@
       <c r="D40" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="33"/>
+      <c r="E40" s="31"/>
       <c r="F40" s="11">
         <v>1</v>
       </c>
-      <c r="G40" s="33"/>
+      <c r="G40" s="31"/>
       <c r="H40" s="11"/>
-      <c r="I40" s="33">
+      <c r="I40" s="31">
         <v>1</v>
       </c>
       <c r="J40" s="11"/>
-      <c r="K40" s="33">
+      <c r="K40" s="31">
         <v>1</v>
       </c>
       <c r="L40" s="11"/>
-      <c r="M40" s="33">
+      <c r="M40" s="31">
         <v>1</v>
       </c>
       <c r="N40" s="11">
         <v>1</v>
       </c>
-      <c r="O40" s="33"/>
+      <c r="O40" s="31"/>
       <c r="P40" s="11"/>
-      <c r="Q40" s="33">
+      <c r="Q40" s="31">
         <v>1</v>
       </c>
       <c r="R40" s="11">
         <v>1</v>
       </c>
-      <c r="S40" s="33"/>
+      <c r="S40" s="31"/>
       <c r="T40" s="11"/>
-      <c r="U40" s="33">
+      <c r="U40" s="31">
         <v>1</v>
       </c>
       <c r="V40" s="11"/>
-      <c r="W40" s="33"/>
+      <c r="W40" s="31"/>
       <c r="X40" s="11"/>
-      <c r="Y40" s="33">
+      <c r="Y40" s="31">
         <v>1</v>
       </c>
       <c r="Z40" s="11">
         <v>1</v>
       </c>
-      <c r="AA40" s="33"/>
+      <c r="AA40" s="31"/>
       <c r="AB40" s="11"/>
-      <c r="AC40" s="33"/>
+      <c r="AC40" s="31"/>
       <c r="AD40" s="11"/>
-      <c r="AE40" s="33"/>
+      <c r="AE40" s="31"/>
       <c r="AF40" s="11"/>
       <c r="AG40" s="13">
         <f t="shared" si="0"/>
@@ -5392,53 +5237,53 @@
       <c r="D41" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="31">
         <v>1</v>
       </c>
       <c r="F41" s="11">
         <v>1</v>
       </c>
-      <c r="G41" s="33"/>
+      <c r="G41" s="31"/>
       <c r="H41" s="11"/>
-      <c r="I41" s="33">
+      <c r="I41" s="31">
         <v>1</v>
       </c>
       <c r="J41" s="11"/>
-      <c r="K41" s="33">
+      <c r="K41" s="31">
         <v>1</v>
       </c>
       <c r="L41" s="11"/>
-      <c r="M41" s="33">
+      <c r="M41" s="31">
         <v>1</v>
       </c>
       <c r="N41" s="11">
         <v>1</v>
       </c>
-      <c r="O41" s="33"/>
+      <c r="O41" s="31"/>
       <c r="P41" s="11"/>
-      <c r="Q41" s="33">
+      <c r="Q41" s="31">
         <v>1</v>
       </c>
       <c r="R41" s="11">
         <v>1</v>
       </c>
-      <c r="S41" s="33"/>
+      <c r="S41" s="31"/>
       <c r="T41" s="11"/>
-      <c r="U41" s="33">
+      <c r="U41" s="31">
         <v>1</v>
       </c>
       <c r="V41" s="11"/>
-      <c r="W41" s="33"/>
+      <c r="W41" s="31"/>
       <c r="X41" s="11"/>
-      <c r="Y41" s="33">
+      <c r="Y41" s="31">
         <v>1</v>
       </c>
       <c r="Z41" s="11"/>
-      <c r="AA41" s="33"/>
+      <c r="AA41" s="31"/>
       <c r="AB41" s="11"/>
-      <c r="AC41" s="33"/>
+      <c r="AC41" s="31"/>
       <c r="AD41" s="11"/>
-      <c r="AE41" s="33"/>
+      <c r="AE41" s="31"/>
       <c r="AF41" s="11"/>
       <c r="AG41" s="13">
         <f t="shared" si="0"/>
@@ -5458,53 +5303,53 @@
       <c r="D42" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="31">
         <v>1</v>
       </c>
       <c r="F42" s="11">
         <v>1</v>
       </c>
-      <c r="G42" s="33"/>
+      <c r="G42" s="31"/>
       <c r="H42" s="11"/>
-      <c r="I42" s="33">
+      <c r="I42" s="31">
         <v>1</v>
       </c>
       <c r="J42" s="11"/>
-      <c r="K42" s="33"/>
+      <c r="K42" s="31"/>
       <c r="L42" s="11"/>
-      <c r="M42" s="33">
+      <c r="M42" s="31">
         <v>1</v>
       </c>
       <c r="N42" s="11">
         <v>1</v>
       </c>
-      <c r="O42" s="33"/>
+      <c r="O42" s="31"/>
       <c r="P42" s="11">
         <v>1</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="Q42" s="31">
         <v>1</v>
       </c>
       <c r="R42" s="11"/>
-      <c r="S42" s="33"/>
+      <c r="S42" s="31"/>
       <c r="T42" s="11"/>
-      <c r="U42" s="33">
+      <c r="U42" s="31">
         <v>1</v>
       </c>
       <c r="V42" s="11"/>
-      <c r="W42" s="33"/>
+      <c r="W42" s="31"/>
       <c r="X42" s="11"/>
-      <c r="Y42" s="33">
+      <c r="Y42" s="31">
         <v>1</v>
       </c>
       <c r="Z42" s="11">
         <v>1</v>
       </c>
-      <c r="AA42" s="33"/>
+      <c r="AA42" s="31"/>
       <c r="AB42" s="11"/>
-      <c r="AC42" s="33"/>
+      <c r="AC42" s="31"/>
       <c r="AD42" s="11"/>
-      <c r="AE42" s="33"/>
+      <c r="AE42" s="31"/>
       <c r="AF42" s="11"/>
       <c r="AG42" s="13">
         <f t="shared" si="0"/>
@@ -5524,53 +5369,53 @@
       <c r="D43" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="33">
+      <c r="E43" s="31">
         <v>1</v>
       </c>
       <c r="F43" s="11">
         <v>1</v>
       </c>
-      <c r="G43" s="33"/>
+      <c r="G43" s="31"/>
       <c r="H43" s="11">
         <v>1</v>
       </c>
-      <c r="I43" s="33">
+      <c r="I43" s="31">
         <v>1</v>
       </c>
       <c r="J43" s="11"/>
-      <c r="K43" s="33"/>
+      <c r="K43" s="31"/>
       <c r="L43" s="11"/>
-      <c r="M43" s="33">
+      <c r="M43" s="31">
         <v>1</v>
       </c>
       <c r="N43" s="11">
         <v>1</v>
       </c>
-      <c r="O43" s="33"/>
+      <c r="O43" s="31"/>
       <c r="P43" s="11">
         <v>1</v>
       </c>
-      <c r="Q43" s="33">
+      <c r="Q43" s="31">
         <v>1</v>
       </c>
       <c r="R43" s="11"/>
-      <c r="S43" s="33"/>
+      <c r="S43" s="31"/>
       <c r="T43" s="11"/>
-      <c r="U43" s="33">
+      <c r="U43" s="31">
         <v>1</v>
       </c>
       <c r="V43" s="11"/>
-      <c r="W43" s="33"/>
+      <c r="W43" s="31"/>
       <c r="X43" s="11"/>
-      <c r="Y43" s="33">
+      <c r="Y43" s="31">
         <v>1</v>
       </c>
       <c r="Z43" s="11"/>
-      <c r="AA43" s="33"/>
+      <c r="AA43" s="31"/>
       <c r="AB43" s="11"/>
-      <c r="AC43" s="33"/>
+      <c r="AC43" s="31"/>
       <c r="AD43" s="11"/>
-      <c r="AE43" s="33"/>
+      <c r="AE43" s="31"/>
       <c r="AF43" s="11"/>
       <c r="AG43" s="13">
         <f t="shared" si="0"/>
@@ -5590,53 +5435,53 @@
       <c r="D44" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="33"/>
+      <c r="E44" s="31"/>
       <c r="F44" s="11">
         <v>1</v>
       </c>
-      <c r="G44" s="33"/>
+      <c r="G44" s="31"/>
       <c r="H44" s="11"/>
-      <c r="I44" s="33">
+      <c r="I44" s="31">
         <v>1</v>
       </c>
       <c r="J44" s="11"/>
-      <c r="K44" s="33"/>
+      <c r="K44" s="31"/>
       <c r="L44" s="11"/>
-      <c r="M44" s="33">
+      <c r="M44" s="31">
         <v>1</v>
       </c>
       <c r="N44" s="11">
         <v>1</v>
       </c>
-      <c r="O44" s="33"/>
+      <c r="O44" s="31"/>
       <c r="P44" s="11"/>
-      <c r="Q44" s="33">
+      <c r="Q44" s="31">
         <v>1</v>
       </c>
       <c r="R44" s="11"/>
-      <c r="S44" s="33"/>
+      <c r="S44" s="31"/>
       <c r="T44" s="11"/>
-      <c r="U44" s="33">
+      <c r="U44" s="31">
         <v>1</v>
       </c>
       <c r="V44" s="11">
         <v>1</v>
       </c>
-      <c r="W44" s="33"/>
+      <c r="W44" s="31"/>
       <c r="X44" s="11"/>
-      <c r="Y44" s="33">
+      <c r="Y44" s="31">
         <v>1</v>
       </c>
       <c r="Z44" s="11">
         <v>1</v>
       </c>
-      <c r="AA44" s="33"/>
+      <c r="AA44" s="31"/>
       <c r="AB44" s="11"/>
-      <c r="AC44" s="33">
+      <c r="AC44" s="31">
         <v>1</v>
       </c>
       <c r="AD44" s="11"/>
-      <c r="AE44" s="33"/>
+      <c r="AE44" s="31"/>
       <c r="AF44" s="11"/>
       <c r="AG44" s="13">
         <f t="shared" si="0"/>
@@ -5656,45 +5501,45 @@
       <c r="D45" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="33"/>
+      <c r="E45" s="31"/>
       <c r="F45" s="11"/>
-      <c r="G45" s="33"/>
+      <c r="G45" s="31"/>
       <c r="H45" s="11">
         <v>1</v>
       </c>
-      <c r="I45" s="33"/>
+      <c r="I45" s="31"/>
       <c r="J45" s="11"/>
-      <c r="K45" s="33"/>
+      <c r="K45" s="31"/>
       <c r="L45" s="11"/>
-      <c r="M45" s="33"/>
+      <c r="M45" s="31"/>
       <c r="N45" s="11"/>
-      <c r="O45" s="33"/>
+      <c r="O45" s="31"/>
       <c r="P45" s="11">
         <v>1</v>
       </c>
-      <c r="Q45" s="33"/>
+      <c r="Q45" s="31"/>
       <c r="R45" s="11"/>
-      <c r="S45" s="33">
+      <c r="S45" s="31">
         <v>1</v>
       </c>
       <c r="T45" s="11">
         <v>1</v>
       </c>
-      <c r="U45" s="33"/>
+      <c r="U45" s="31"/>
       <c r="V45" s="11"/>
-      <c r="W45" s="33"/>
+      <c r="W45" s="31"/>
       <c r="X45" s="11">
         <v>1</v>
       </c>
-      <c r="Y45" s="33"/>
+      <c r="Y45" s="31"/>
       <c r="Z45" s="11"/>
-      <c r="AA45" s="33">
+      <c r="AA45" s="31">
         <v>1</v>
       </c>
       <c r="AB45" s="11"/>
-      <c r="AC45" s="33"/>
+      <c r="AC45" s="31"/>
       <c r="AD45" s="11"/>
-      <c r="AE45" s="33"/>
+      <c r="AE45" s="31"/>
       <c r="AF45" s="11"/>
       <c r="AG45" s="13">
         <f t="shared" si="0"/>
@@ -5714,51 +5559,51 @@
       <c r="D46" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E46" s="33">
+      <c r="E46" s="31">
         <v>1</v>
       </c>
       <c r="F46" s="11"/>
-      <c r="G46" s="33"/>
+      <c r="G46" s="31"/>
       <c r="H46" s="11">
         <v>1</v>
       </c>
-      <c r="I46" s="33"/>
+      <c r="I46" s="31"/>
       <c r="J46" s="11">
         <v>1</v>
       </c>
-      <c r="K46" s="33"/>
+      <c r="K46" s="31"/>
       <c r="L46" s="11"/>
-      <c r="M46" s="33"/>
+      <c r="M46" s="31"/>
       <c r="N46" s="11"/>
-      <c r="O46" s="33"/>
+      <c r="O46" s="31"/>
       <c r="P46" s="11"/>
-      <c r="Q46" s="33">
+      <c r="Q46" s="31">
         <v>1</v>
       </c>
       <c r="R46" s="11"/>
-      <c r="S46" s="33"/>
+      <c r="S46" s="31"/>
       <c r="T46" s="11"/>
-      <c r="U46" s="33">
+      <c r="U46" s="31">
         <v>1</v>
       </c>
       <c r="V46" s="11"/>
-      <c r="W46" s="33"/>
+      <c r="W46" s="31"/>
       <c r="X46" s="11"/>
-      <c r="Y46" s="33">
+      <c r="Y46" s="31">
         <v>1</v>
       </c>
       <c r="Z46" s="11">
         <v>1</v>
       </c>
-      <c r="AA46" s="33">
+      <c r="AA46" s="31">
         <v>1</v>
       </c>
       <c r="AB46" s="11"/>
-      <c r="AC46" s="33">
+      <c r="AC46" s="31">
         <v>1</v>
       </c>
       <c r="AD46" s="11"/>
-      <c r="AE46" s="33"/>
+      <c r="AE46" s="31"/>
       <c r="AF46" s="11"/>
       <c r="AG46" s="13">
         <f t="shared" si="0"/>
@@ -5778,51 +5623,51 @@
       <c r="D47" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E47" s="33"/>
+      <c r="E47" s="31"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="33"/>
+      <c r="G47" s="31"/>
       <c r="H47" s="11"/>
-      <c r="I47" s="33"/>
+      <c r="I47" s="31"/>
       <c r="J47" s="11">
         <v>1</v>
       </c>
-      <c r="K47" s="33"/>
+      <c r="K47" s="31"/>
       <c r="L47" s="11"/>
-      <c r="M47" s="33"/>
+      <c r="M47" s="31"/>
       <c r="N47" s="11"/>
-      <c r="O47" s="33"/>
+      <c r="O47" s="31"/>
       <c r="P47" s="11">
         <v>1</v>
       </c>
-      <c r="Q47" s="33">
+      <c r="Q47" s="31">
         <v>1</v>
       </c>
       <c r="R47" s="11"/>
-      <c r="S47" s="33"/>
+      <c r="S47" s="31"/>
       <c r="T47" s="11">
         <v>1</v>
       </c>
-      <c r="U47" s="33">
+      <c r="U47" s="31">
         <v>1</v>
       </c>
       <c r="V47" s="11"/>
-      <c r="W47" s="33"/>
+      <c r="W47" s="31"/>
       <c r="X47" s="11"/>
-      <c r="Y47" s="33">
+      <c r="Y47" s="31">
         <v>1</v>
       </c>
       <c r="Z47" s="11">
         <v>1</v>
       </c>
-      <c r="AA47" s="33">
+      <c r="AA47" s="31">
         <v>1</v>
       </c>
       <c r="AB47" s="11"/>
-      <c r="AC47" s="33">
+      <c r="AC47" s="31">
         <v>1</v>
       </c>
       <c r="AD47" s="11"/>
-      <c r="AE47" s="33"/>
+      <c r="AE47" s="31"/>
       <c r="AF47" s="11"/>
       <c r="AG47" s="13">
         <f t="shared" si="0"/>
@@ -5842,51 +5687,51 @@
       <c r="D48" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="31">
         <v>1</v>
       </c>
       <c r="F48" s="11"/>
-      <c r="G48" s="33">
+      <c r="G48" s="31">
         <v>1</v>
       </c>
       <c r="H48" s="11">
         <v>1</v>
       </c>
-      <c r="I48" s="33"/>
+      <c r="I48" s="31"/>
       <c r="J48" s="11">
         <v>1</v>
       </c>
-      <c r="K48" s="33"/>
+      <c r="K48" s="31"/>
       <c r="L48" s="11">
         <v>1</v>
       </c>
-      <c r="M48" s="33"/>
+      <c r="M48" s="31"/>
       <c r="N48" s="11"/>
-      <c r="O48" s="33">
+      <c r="O48" s="31">
         <v>1</v>
       </c>
       <c r="P48" s="11">
         <v>1</v>
       </c>
-      <c r="Q48" s="33">
+      <c r="Q48" s="31">
         <v>1</v>
       </c>
       <c r="R48" s="11"/>
-      <c r="S48" s="33"/>
+      <c r="S48" s="31"/>
       <c r="T48" s="11"/>
-      <c r="U48" s="33">
+      <c r="U48" s="31">
         <v>1</v>
       </c>
       <c r="V48" s="11"/>
-      <c r="W48" s="33"/>
+      <c r="W48" s="31"/>
       <c r="X48" s="11"/>
-      <c r="Y48" s="33"/>
+      <c r="Y48" s="31"/>
       <c r="Z48" s="11"/>
-      <c r="AA48" s="33"/>
+      <c r="AA48" s="31"/>
       <c r="AB48" s="11"/>
-      <c r="AC48" s="33"/>
+      <c r="AC48" s="31"/>
       <c r="AD48" s="11"/>
-      <c r="AE48" s="33"/>
+      <c r="AE48" s="31"/>
       <c r="AF48" s="11"/>
       <c r="AG48" s="13">
         <f t="shared" si="0"/>
@@ -5906,51 +5751,51 @@
       <c r="D49" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E49" s="33"/>
+      <c r="E49" s="31"/>
       <c r="F49" s="11">
         <v>1</v>
       </c>
-      <c r="G49" s="33"/>
+      <c r="G49" s="31"/>
       <c r="H49" s="11"/>
-      <c r="I49" s="33"/>
+      <c r="I49" s="31"/>
       <c r="J49" s="11">
         <v>1</v>
       </c>
-      <c r="K49" s="33"/>
+      <c r="K49" s="31"/>
       <c r="L49" s="11">
         <v>1</v>
       </c>
-      <c r="M49" s="33"/>
+      <c r="M49" s="31"/>
       <c r="N49" s="11"/>
-      <c r="O49" s="33"/>
+      <c r="O49" s="31"/>
       <c r="P49" s="11"/>
-      <c r="Q49" s="33">
+      <c r="Q49" s="31">
         <v>1</v>
       </c>
       <c r="R49" s="11"/>
-      <c r="S49" s="33"/>
+      <c r="S49" s="31"/>
       <c r="T49" s="11">
         <v>1</v>
       </c>
-      <c r="U49" s="33">
+      <c r="U49" s="31">
         <v>1</v>
       </c>
       <c r="V49" s="11">
         <v>1</v>
       </c>
-      <c r="W49" s="33"/>
+      <c r="W49" s="31"/>
       <c r="X49" s="11"/>
-      <c r="Y49" s="33">
+      <c r="Y49" s="31">
         <v>1</v>
       </c>
       <c r="Z49" s="11"/>
-      <c r="AA49" s="33">
+      <c r="AA49" s="31">
         <v>1</v>
       </c>
       <c r="AB49" s="11"/>
-      <c r="AC49" s="33"/>
+      <c r="AC49" s="31"/>
       <c r="AD49" s="11"/>
-      <c r="AE49" s="33"/>
+      <c r="AE49" s="31"/>
       <c r="AF49" s="11"/>
       <c r="AG49" s="13">
         <f t="shared" si="0"/>
@@ -5970,49 +5815,49 @@
       <c r="D50" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="31">
         <v>1</v>
       </c>
       <c r="F50" s="11"/>
-      <c r="G50" s="33"/>
+      <c r="G50" s="31"/>
       <c r="H50" s="11">
         <v>1</v>
       </c>
-      <c r="I50" s="33"/>
+      <c r="I50" s="31"/>
       <c r="J50" s="11">
         <v>1</v>
       </c>
-      <c r="K50" s="33"/>
+      <c r="K50" s="31"/>
       <c r="L50" s="11">
         <v>1</v>
       </c>
-      <c r="M50" s="33"/>
+      <c r="M50" s="31"/>
       <c r="N50" s="11"/>
-      <c r="O50" s="33"/>
+      <c r="O50" s="31"/>
       <c r="P50" s="11">
         <v>1</v>
       </c>
-      <c r="Q50" s="33"/>
+      <c r="Q50" s="31"/>
       <c r="R50" s="11"/>
-      <c r="S50" s="33"/>
+      <c r="S50" s="31"/>
       <c r="T50" s="11"/>
-      <c r="U50" s="33"/>
+      <c r="U50" s="31"/>
       <c r="V50" s="11"/>
-      <c r="W50" s="33"/>
+      <c r="W50" s="31"/>
       <c r="X50" s="11"/>
-      <c r="Y50" s="33">
+      <c r="Y50" s="31">
         <v>1</v>
       </c>
       <c r="Z50" s="11">
         <v>1</v>
       </c>
-      <c r="AA50" s="33">
+      <c r="AA50" s="31">
         <v>1</v>
       </c>
       <c r="AB50" s="11"/>
-      <c r="AC50" s="33"/>
+      <c r="AC50" s="31"/>
       <c r="AD50" s="11"/>
-      <c r="AE50" s="33">
+      <c r="AE50" s="31">
         <v>1</v>
       </c>
       <c r="AF50" s="11"/>
@@ -6178,111 +6023,111 @@
   <dimension ref="A1:AJ7"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.1640625" style="60" customWidth="1"/>
-    <col min="2" max="2" width="29.6640625" style="60" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="60" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" style="60" customWidth="1"/>
-    <col min="5" max="32" width="5.33203125" style="69" customWidth="1"/>
-    <col min="33" max="36" width="8.83203125" style="59"/>
-    <col min="37" max="16384" width="8.83203125" style="60"/>
+    <col min="1" max="1" width="4.1640625" style="58" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" style="58" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="58" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" style="58" customWidth="1"/>
+    <col min="5" max="32" width="5.33203125" style="67" customWidth="1"/>
+    <col min="33" max="36" width="8.83203125" style="57"/>
+    <col min="37" max="16384" width="8.83203125" style="58"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="3" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="74"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="73"/>
       <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
     </row>
     <row r="2" spans="1:36" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="71">
+      <c r="E2" s="70">
         <v>46180</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71">
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70">
         <v>46181</v>
       </c>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71">
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70">
         <v>46182</v>
       </c>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71">
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70">
         <v>46183</v>
       </c>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71">
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70">
         <v>46184</v>
       </c>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71">
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
+      <c r="Y2" s="70">
         <v>46187</v>
       </c>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71">
+      <c r="Z2" s="70"/>
+      <c r="AA2" s="70"/>
+      <c r="AB2" s="70"/>
+      <c r="AC2" s="70">
         <v>46188</v>
       </c>
-      <c r="AD2" s="71"/>
-      <c r="AE2" s="71"/>
-      <c r="AF2" s="71"/>
-      <c r="AG2" s="72" t="s">
+      <c r="AD2" s="70"/>
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="71" t="s">
         <v>63</v>
       </c>
       <c r="AH2" s="1"/>
@@ -6290,503 +6135,503 @@
       <c r="AJ2" s="2"/>
     </row>
     <row r="3" spans="1:36" s="3" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="32">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="F3" s="7">
         <v>11</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="30">
         <v>12.3</v>
       </c>
       <c r="H3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="J3" s="7">
         <v>11</v>
       </c>
-      <c r="K3" s="32">
+      <c r="K3" s="30">
         <v>12.3</v>
       </c>
       <c r="L3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M3" s="32">
+      <c r="M3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="N3" s="7">
         <v>11</v>
       </c>
-      <c r="O3" s="32">
+      <c r="O3" s="30">
         <v>12.3</v>
       </c>
       <c r="P3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Q3" s="32">
+      <c r="Q3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="R3" s="7">
         <v>11</v>
       </c>
-      <c r="S3" s="32">
+      <c r="S3" s="30">
         <v>12.3</v>
       </c>
       <c r="T3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="U3" s="32">
+      <c r="U3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="V3" s="7">
         <v>11</v>
       </c>
-      <c r="W3" s="32">
+      <c r="W3" s="30">
         <v>12.3</v>
       </c>
       <c r="X3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Y3" s="32">
+      <c r="Y3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="Z3" s="7">
         <v>11</v>
       </c>
-      <c r="AA3" s="32">
+      <c r="AA3" s="30">
         <v>12.3</v>
       </c>
       <c r="AB3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AC3" s="32">
+      <c r="AC3" s="30">
         <v>9.3000000000000007</v>
       </c>
       <c r="AD3" s="7">
         <v>11</v>
       </c>
-      <c r="AE3" s="32">
+      <c r="AE3" s="30">
         <v>12.3</v>
       </c>
       <c r="AF3" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AG3" s="72"/>
+      <c r="AG3" s="71"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="2"/>
       <c r="AJ3" s="2"/>
     </row>
-    <row r="4" spans="1:36" s="59" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="61">
-        <v>1</v>
-      </c>
-      <c r="B4" s="62" t="s">
+    <row r="4" spans="1:36" s="57" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="59">
+        <v>1</v>
+      </c>
+      <c r="B4" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="64">
-        <v>1</v>
-      </c>
-      <c r="F4" s="64">
-        <v>1</v>
-      </c>
-      <c r="G4" s="64">
-        <v>1</v>
-      </c>
-      <c r="H4" s="64">
-        <v>1</v>
-      </c>
-      <c r="I4" s="64">
-        <v>1</v>
-      </c>
-      <c r="J4" s="64">
-        <v>1</v>
-      </c>
-      <c r="K4" s="64">
-        <v>1</v>
-      </c>
-      <c r="L4" s="64">
-        <v>1</v>
-      </c>
-      <c r="M4" s="64">
-        <v>1</v>
-      </c>
-      <c r="N4" s="64">
-        <v>1</v>
-      </c>
-      <c r="O4" s="64">
-        <v>1</v>
-      </c>
-      <c r="P4" s="64">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="64">
-        <v>1</v>
-      </c>
-      <c r="R4" s="64">
-        <v>1</v>
-      </c>
-      <c r="S4" s="64">
-        <v>1</v>
-      </c>
-      <c r="T4" s="64">
-        <v>1</v>
-      </c>
-      <c r="U4" s="64">
-        <v>1</v>
-      </c>
-      <c r="V4" s="64">
-        <v>1</v>
-      </c>
-      <c r="W4" s="64">
-        <v>1</v>
-      </c>
-      <c r="X4" s="64">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="64">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="64">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="64">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="64">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="64">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="64">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="64">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="64">
-        <v>1</v>
-      </c>
-      <c r="AG4" s="65">
+      <c r="E4" s="62">
+        <v>1</v>
+      </c>
+      <c r="F4" s="62">
+        <v>1</v>
+      </c>
+      <c r="G4" s="62">
+        <v>1</v>
+      </c>
+      <c r="H4" s="62">
+        <v>1</v>
+      </c>
+      <c r="I4" s="62">
+        <v>1</v>
+      </c>
+      <c r="J4" s="62">
+        <v>1</v>
+      </c>
+      <c r="K4" s="62">
+        <v>1</v>
+      </c>
+      <c r="L4" s="62">
+        <v>1</v>
+      </c>
+      <c r="M4" s="62">
+        <v>1</v>
+      </c>
+      <c r="N4" s="62">
+        <v>1</v>
+      </c>
+      <c r="O4" s="62">
+        <v>1</v>
+      </c>
+      <c r="P4" s="62">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="62">
+        <v>1</v>
+      </c>
+      <c r="R4" s="62">
+        <v>1</v>
+      </c>
+      <c r="S4" s="62">
+        <v>1</v>
+      </c>
+      <c r="T4" s="62">
+        <v>1</v>
+      </c>
+      <c r="U4" s="62">
+        <v>1</v>
+      </c>
+      <c r="V4" s="62">
+        <v>1</v>
+      </c>
+      <c r="W4" s="62">
+        <v>1</v>
+      </c>
+      <c r="X4" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="62">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="62">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="62">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="62">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="62">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="62">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="62">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="62">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="63">
         <f>SUM(E4:AF4)</f>
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="59" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="66">
+    <row r="5" spans="1:36" s="57" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="64">
         <v>2</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="64">
-        <v>1</v>
-      </c>
-      <c r="F5" s="64">
-        <v>1</v>
-      </c>
-      <c r="G5" s="64">
-        <v>1</v>
-      </c>
-      <c r="H5" s="64">
-        <v>1</v>
-      </c>
-      <c r="I5" s="64">
-        <v>1</v>
-      </c>
-      <c r="J5" s="64">
-        <v>1</v>
-      </c>
-      <c r="K5" s="64">
-        <v>1</v>
-      </c>
-      <c r="L5" s="64">
-        <v>1</v>
-      </c>
-      <c r="M5" s="64">
-        <v>1</v>
-      </c>
-      <c r="N5" s="64">
-        <v>1</v>
-      </c>
-      <c r="O5" s="64">
-        <v>1</v>
-      </c>
-      <c r="P5" s="64">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="64">
-        <v>1</v>
-      </c>
-      <c r="R5" s="64">
-        <v>1</v>
-      </c>
-      <c r="S5" s="64">
-        <v>1</v>
-      </c>
-      <c r="T5" s="64">
-        <v>1</v>
-      </c>
-      <c r="U5" s="64">
-        <v>1</v>
-      </c>
-      <c r="V5" s="64">
-        <v>1</v>
-      </c>
-      <c r="W5" s="64">
-        <v>1</v>
-      </c>
-      <c r="X5" s="64">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="64">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="64">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="64">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="64">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="64">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="64">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="64">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="64">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="68">
+      <c r="E5" s="62">
+        <v>1</v>
+      </c>
+      <c r="F5" s="62">
+        <v>1</v>
+      </c>
+      <c r="G5" s="62">
+        <v>1</v>
+      </c>
+      <c r="H5" s="62">
+        <v>1</v>
+      </c>
+      <c r="I5" s="62">
+        <v>1</v>
+      </c>
+      <c r="J5" s="62">
+        <v>1</v>
+      </c>
+      <c r="K5" s="62">
+        <v>1</v>
+      </c>
+      <c r="L5" s="62">
+        <v>1</v>
+      </c>
+      <c r="M5" s="62">
+        <v>1</v>
+      </c>
+      <c r="N5" s="62">
+        <v>1</v>
+      </c>
+      <c r="O5" s="62">
+        <v>1</v>
+      </c>
+      <c r="P5" s="62">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="62">
+        <v>1</v>
+      </c>
+      <c r="R5" s="62">
+        <v>1</v>
+      </c>
+      <c r="S5" s="62">
+        <v>1</v>
+      </c>
+      <c r="T5" s="62">
+        <v>1</v>
+      </c>
+      <c r="U5" s="62">
+        <v>1</v>
+      </c>
+      <c r="V5" s="62">
+        <v>1</v>
+      </c>
+      <c r="W5" s="62">
+        <v>1</v>
+      </c>
+      <c r="X5" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="62">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="62">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="62">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="62">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="62">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="62">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="62">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="62">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="66">
         <f t="shared" ref="AG5:AG7" si="0">SUM(E5:AF5)</f>
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:36" s="59" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61">
+    <row r="6" spans="1:36" s="57" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="59">
         <v>3</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64">
-        <v>1</v>
-      </c>
-      <c r="F6" s="64">
-        <v>1</v>
-      </c>
-      <c r="G6" s="64">
-        <v>1</v>
-      </c>
-      <c r="H6" s="64">
-        <v>1</v>
-      </c>
-      <c r="I6" s="64">
-        <v>1</v>
-      </c>
-      <c r="J6" s="64">
-        <v>1</v>
-      </c>
-      <c r="K6" s="64">
-        <v>1</v>
-      </c>
-      <c r="L6" s="64">
-        <v>1</v>
-      </c>
-      <c r="M6" s="64">
-        <v>1</v>
-      </c>
-      <c r="N6" s="64">
-        <v>1</v>
-      </c>
-      <c r="O6" s="64">
-        <v>1</v>
-      </c>
-      <c r="P6" s="64">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="64">
-        <v>1</v>
-      </c>
-      <c r="R6" s="64">
-        <v>1</v>
-      </c>
-      <c r="S6" s="64">
-        <v>1</v>
-      </c>
-      <c r="T6" s="64">
-        <v>1</v>
-      </c>
-      <c r="U6" s="64">
-        <v>1</v>
-      </c>
-      <c r="V6" s="64">
-        <v>1</v>
-      </c>
-      <c r="W6" s="64">
-        <v>1</v>
-      </c>
-      <c r="X6" s="64">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="64">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="64">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="64">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="64">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="64">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="64">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="64">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="64">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="68">
+      <c r="E6" s="62">
+        <v>1</v>
+      </c>
+      <c r="F6" s="62">
+        <v>1</v>
+      </c>
+      <c r="G6" s="62">
+        <v>1</v>
+      </c>
+      <c r="H6" s="62">
+        <v>1</v>
+      </c>
+      <c r="I6" s="62">
+        <v>1</v>
+      </c>
+      <c r="J6" s="62">
+        <v>1</v>
+      </c>
+      <c r="K6" s="62">
+        <v>1</v>
+      </c>
+      <c r="L6" s="62">
+        <v>1</v>
+      </c>
+      <c r="M6" s="62">
+        <v>1</v>
+      </c>
+      <c r="N6" s="62">
+        <v>1</v>
+      </c>
+      <c r="O6" s="62">
+        <v>1</v>
+      </c>
+      <c r="P6" s="62">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="62">
+        <v>1</v>
+      </c>
+      <c r="R6" s="62">
+        <v>1</v>
+      </c>
+      <c r="S6" s="62">
+        <v>1</v>
+      </c>
+      <c r="T6" s="62">
+        <v>1</v>
+      </c>
+      <c r="U6" s="62">
+        <v>1</v>
+      </c>
+      <c r="V6" s="62">
+        <v>1</v>
+      </c>
+      <c r="W6" s="62">
+        <v>1</v>
+      </c>
+      <c r="X6" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="62">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="62">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="62">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="62">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="62">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="62">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="62">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="62">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="66">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:36" s="59" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="66">
+    <row r="7" spans="1:36" s="57" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="64">
-        <v>1</v>
-      </c>
-      <c r="F7" s="64">
-        <v>1</v>
-      </c>
-      <c r="G7" s="64">
-        <v>1</v>
-      </c>
-      <c r="H7" s="64">
-        <v>1</v>
-      </c>
-      <c r="I7" s="64">
-        <v>1</v>
-      </c>
-      <c r="J7" s="64">
-        <v>1</v>
-      </c>
-      <c r="K7" s="64">
-        <v>1</v>
-      </c>
-      <c r="L7" s="64">
-        <v>1</v>
-      </c>
-      <c r="M7" s="64">
-        <v>1</v>
-      </c>
-      <c r="N7" s="64">
-        <v>1</v>
-      </c>
-      <c r="O7" s="64">
-        <v>1</v>
-      </c>
-      <c r="P7" s="64">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="64">
-        <v>1</v>
-      </c>
-      <c r="R7" s="64">
-        <v>1</v>
-      </c>
-      <c r="S7" s="64">
-        <v>1</v>
-      </c>
-      <c r="T7" s="64">
-        <v>1</v>
-      </c>
-      <c r="U7" s="64">
-        <v>1</v>
-      </c>
-      <c r="V7" s="64">
-        <v>1</v>
-      </c>
-      <c r="W7" s="64">
-        <v>1</v>
-      </c>
-      <c r="X7" s="64">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="64">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="64">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="64">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="64">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="64">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="64">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="64">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="64">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="68">
+      <c r="E7" s="62">
+        <v>1</v>
+      </c>
+      <c r="F7" s="62">
+        <v>1</v>
+      </c>
+      <c r="G7" s="62">
+        <v>1</v>
+      </c>
+      <c r="H7" s="62">
+        <v>1</v>
+      </c>
+      <c r="I7" s="62">
+        <v>1</v>
+      </c>
+      <c r="J7" s="62">
+        <v>1</v>
+      </c>
+      <c r="K7" s="62">
+        <v>1</v>
+      </c>
+      <c r="L7" s="62">
+        <v>1</v>
+      </c>
+      <c r="M7" s="62">
+        <v>1</v>
+      </c>
+      <c r="N7" s="62">
+        <v>1</v>
+      </c>
+      <c r="O7" s="62">
+        <v>1</v>
+      </c>
+      <c r="P7" s="62">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="62">
+        <v>1</v>
+      </c>
+      <c r="R7" s="62">
+        <v>1</v>
+      </c>
+      <c r="S7" s="62">
+        <v>1</v>
+      </c>
+      <c r="T7" s="62">
+        <v>1</v>
+      </c>
+      <c r="U7" s="62">
+        <v>1</v>
+      </c>
+      <c r="V7" s="62">
+        <v>1</v>
+      </c>
+      <c r="W7" s="62">
+        <v>1</v>
+      </c>
+      <c r="X7" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="62">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="62">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="62">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="62">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="62">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="62">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="62">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="62">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="66">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>

--- a/Duty Roaster for Mid Term.xlsx
+++ b/Duty Roaster for Mid Term.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Control Room NPI\MID TERM JUNE-2026\Gemini Duty Roster  Teacher list,hall super\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Duty Roaster\duty-roater-finder-ngpi-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64D1A3B-9B4A-4CFF-A389-F049F64FEBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="All Chief Invigilators" sheetId="8" r:id="rId1"/>
@@ -25,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'MLSS Roaster'!$A$2:$C$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'All Teachers'!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -97,9 +96,6 @@
   </si>
   <si>
     <t>Mr.Mohammed Zinder Hossain Khan</t>
-  </si>
-  <si>
-    <t>Mr.Syeda Farida Pervin</t>
   </si>
   <si>
     <t>Mr.Quazi Adnan Ibna Quayum</t>
@@ -414,11 +410,14 @@
       <t>Duty Roster for All Invigilators</t>
     </r>
   </si>
+  <si>
+    <t>Ms. Syeda Farida Pervin</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0000"/>
     <numFmt numFmtId="165" formatCode="00.00"/>
@@ -952,9 +951,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -992,9 +991,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1029,7 +1028,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1064,7 +1063,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1237,7 +1236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D52BD145-3CE8-48D6-A3C8-413275DA2782}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1255,7 +1254,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -1301,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="70">
         <v>46180</v>
@@ -1346,7 +1345,7 @@
       <c r="AE2" s="70"/>
       <c r="AF2" s="70"/>
       <c r="AG2" s="71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
@@ -1447,13 +1446,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="68" t="s">
         <v>77</v>
-      </c>
-      <c r="D4" s="68" t="s">
-        <v>78</v>
       </c>
       <c r="E4" s="46">
         <v>1</v>
@@ -1523,13 +1522,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" s="47"/>
       <c r="F5" s="40"/>
@@ -1717,7 +1716,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C5" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A2:C5"/>
   <mergeCells count="13">
     <mergeCell ref="Y2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
@@ -1744,7 +1743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4DFF899-26E7-409B-80D8-6B3F43797761}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1762,7 +1761,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -1808,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="70">
         <v>46180</v>
@@ -1853,7 +1852,7 @@
       <c r="AE2" s="70"/>
       <c r="AF2" s="70"/>
       <c r="AG2" s="71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
@@ -1954,10 +1953,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>64</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>65</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>2</v>
@@ -2028,10 +2027,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>5</v>
@@ -2102,10 +2101,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>3</v>
@@ -2176,13 +2175,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="D7" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" s="49">
         <v>1</v>
@@ -2250,13 +2249,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" s="50">
         <v>1</v>
@@ -2324,7 +2323,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>6</v>
@@ -2398,10 +2397,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>4</v>
@@ -2472,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>6</v>
@@ -2664,8 +2663,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C11" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C11">
+  <autoFilter ref="A2:C11">
+    <sortState ref="A5:C11">
       <sortCondition ref="C2:C11"/>
     </sortState>
   </autoFilter>
@@ -2695,7 +2694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6A6B97-BFE2-4416-BC37-FB9C281BD0CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2713,7 +2712,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -2759,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="70">
         <v>46180</v>
@@ -2804,7 +2803,7 @@
       <c r="AE2" s="70"/>
       <c r="AF2" s="70"/>
       <c r="AG2" s="71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
@@ -2966,7 +2965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -2977,7 +2976,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="11"/>
@@ -3025,7 +3024,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>6</v>
@@ -3087,7 +3086,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>6</v>
@@ -3145,7 +3144,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>6</v>
@@ -3203,7 +3202,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>6</v>
@@ -3255,7 +3254,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>6</v>
@@ -3319,7 +3318,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>6</v>
@@ -3385,13 +3384,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" s="31">
         <v>1</v>
@@ -3451,13 +3450,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="11"/>
@@ -3513,13 +3512,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="11"/>
@@ -3573,13 +3572,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" s="33"/>
       <c r="F15" s="11"/>
@@ -3635,13 +3634,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" s="33"/>
       <c r="F16" s="11"/>
@@ -3689,13 +3688,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" s="31">
         <v>1</v>
@@ -3753,13 +3752,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" s="31">
         <v>1</v>
@@ -3815,7 +3814,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>9</v>
@@ -3881,7 +3880,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>9</v>
@@ -3947,7 +3946,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>9</v>
@@ -4013,7 +4012,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>9</v>
@@ -4075,7 +4074,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>9</v>
@@ -4139,7 +4138,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>9</v>
@@ -4201,7 +4200,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>9</v>
@@ -4263,7 +4262,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>9</v>
@@ -4323,7 +4322,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>9</v>
@@ -4373,7 +4372,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>9</v>
@@ -4439,7 +4438,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>9</v>
@@ -4505,7 +4504,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>9</v>
@@ -4571,7 +4570,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>9</v>
@@ -4637,7 +4636,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>9</v>
@@ -4703,7 +4702,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>9</v>
@@ -4769,7 +4768,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>9</v>
@@ -4835,7 +4834,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>9</v>
@@ -4901,7 +4900,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>9</v>
@@ -4967,7 +4966,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="35" t="s">
         <v>9</v>
@@ -5031,7 +5030,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>9</v>
@@ -5097,7 +5096,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>9</v>
@@ -5163,7 +5162,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>9</v>
@@ -5229,7 +5228,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>9</v>
@@ -5295,7 +5294,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>9</v>
@@ -5361,7 +5360,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>9</v>
@@ -5427,7 +5426,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>12</v>
@@ -5493,7 +5492,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>11</v>
@@ -5551,7 +5550,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>7</v>
@@ -5615,7 +5614,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>7</v>
@@ -5679,7 +5678,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>7</v>
@@ -5743,7 +5742,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>7</v>
@@ -5807,7 +5806,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>7</v>
@@ -5985,8 +5984,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C44" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C44">
+  <autoFilter ref="A2:C44">
+    <sortState ref="A5:C44">
       <sortCondition ref="C2:C44"/>
     </sortState>
   </autoFilter>
@@ -6016,7 +6015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16130596-EFCB-41C1-ADDC-89014A501738}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6034,7 +6033,7 @@
   <sheetData>
     <row r="1" spans="1:36" s="3" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -6083,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="70">
         <v>46180</v>
@@ -6128,7 +6127,7 @@
       <c r="AE2" s="70"/>
       <c r="AF2" s="70"/>
       <c r="AG2" s="71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
@@ -6233,10 +6232,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="61" t="s">
         <v>80</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>81</v>
       </c>
       <c r="D4" s="66" t="s">
         <v>3</v>
@@ -6335,10 +6334,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D5" s="66" t="s">
         <v>4</v>
@@ -6437,10 +6436,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D6" s="66" t="s">
         <v>2</v>
@@ -6539,10 +6538,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" s="66" t="s">
         <v>5</v>
@@ -6637,8 +6636,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C7" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C7">
+  <autoFilter ref="A2:C7">
+    <sortState ref="A5:C7">
       <sortCondition ref="C2:C7"/>
     </sortState>
   </autoFilter>
